--- a/data/xlsx/cleaned_gpr.xlsx
+++ b/data/xlsx/cleaned_gpr.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Desktop\dse\projects_2nd_year\time_series\ts_macchi_wang\data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{FEE3925D-0AD9-43D2-8B7E-BA0206EB2652}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EE746FE-294A-4767-B6B1-FD3041D91DBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{7F69F110-EA51-4D9B-B5FC-E340E0CAEE3A}"/>
   </bookViews>
@@ -33,10 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="762" uniqueCount="49">
-  <si>
-    <t>month</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
   <si>
     <t>GPR</t>
   </si>
@@ -179,7 +176,7 @@
     <t>GPRC_ZAF</t>
   </si>
   <si>
-    <t/>
+    <t>date</t>
   </si>
 </sst>
 </file>
@@ -551,159 +548,159 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B405E34-1EE5-4B68-A9E8-D5084A085D26}">
-  <dimension ref="A1:BA358"/>
+  <dimension ref="A1:AV358"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AE1" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AF1" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AG1" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AH1" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AI1" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AJ1" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AK1" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AL1" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AM1" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AN1" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AO1" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AP1" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AQ1" t="s">
         <v>41</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AR1" t="s">
         <v>42</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AS1" t="s">
         <v>43</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AT1" t="s">
         <v>44</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AU1" t="s">
         <v>45</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AV1" t="s">
         <v>46</v>
       </c>
-      <c r="AV1" t="s">
-        <v>47</v>
-      </c>
     </row>
-    <row r="2" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>35065</v>
       </c>
@@ -848,22 +845,8 @@
       <c r="AV2" s="2">
         <v>3.7999697029590607E-2</v>
       </c>
-      <c r="AW2" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX2" t="s">
-        <v>48</v>
-      </c>
-      <c r="AZ2">
-        <f>(C2/AVERAGE(C2:C358)*100)</f>
-        <v>73.905602019636859</v>
-      </c>
-      <c r="BA2">
-        <f>(L2/AVERAGE(L2:L358))*100</f>
-        <v>38.563582194911689</v>
-      </c>
     </row>
-    <row r="3" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>35096</v>
       </c>
@@ -1008,18 +991,8 @@
       <c r="AV3" s="2">
         <v>4.3784581124782562E-2</v>
       </c>
-      <c r="AW3" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX3" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA3">
-        <f t="shared" ref="BA3:BA66" si="0">(L3/AVERAGE(L3:L359))*100</f>
-        <v>73.318612337602943</v>
-      </c>
     </row>
-    <row r="4" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>35125</v>
       </c>
@@ -1164,18 +1137,8 @@
       <c r="AV4" s="2">
         <v>1.4688062481582165E-2</v>
       </c>
-      <c r="AW4" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX4" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA4">
-        <f t="shared" si="0"/>
-        <v>71.64235011623478</v>
-      </c>
     </row>
-    <row r="5" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>35156</v>
       </c>
@@ -1320,18 +1283,8 @@
       <c r="AV5" s="2">
         <v>3.9942484349012375E-2</v>
       </c>
-      <c r="AW5" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX5" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA5">
-        <f t="shared" si="0"/>
-        <v>66.84795871964964</v>
-      </c>
     </row>
-    <row r="6" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>35186</v>
       </c>
@@ -1476,18 +1429,8 @@
       <c r="AV6" s="2">
         <v>2.196112833917141E-2</v>
       </c>
-      <c r="AW6" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX6" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA6">
-        <f t="shared" si="0"/>
-        <v>55.146922580697591</v>
-      </c>
     </row>
-    <row r="7" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>35217</v>
       </c>
@@ -1632,18 +1575,8 @@
       <c r="AV7" s="2">
         <v>4.8758402466773987E-2</v>
       </c>
-      <c r="AW7" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX7" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA7">
-        <f t="shared" si="0"/>
-        <v>51.767529460434204</v>
-      </c>
     </row>
-    <row r="8" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>35247</v>
       </c>
@@ -1788,18 +1721,8 @@
       <c r="AV8" s="2">
         <v>4.428848996758461E-2</v>
       </c>
-      <c r="AW8" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX8" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA8">
-        <f t="shared" si="0"/>
-        <v>35.585817676528521</v>
-      </c>
     </row>
-    <row r="9" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>35278</v>
       </c>
@@ -1944,18 +1867,8 @@
       <c r="AV9" s="2">
         <v>8.8901534676551819E-2</v>
       </c>
-      <c r="AW9" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX9" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA9">
-        <f t="shared" si="0"/>
-        <v>35.125220881546802</v>
-      </c>
     </row>
-    <row r="10" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>35309</v>
       </c>
@@ -2100,18 +2013,8 @@
       <c r="AV10" s="2">
         <v>6.6410861909389496E-2</v>
       </c>
-      <c r="AW10" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX10" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA10">
-        <f t="shared" si="0"/>
-        <v>41.090928095114307</v>
-      </c>
     </row>
-    <row r="11" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>35339</v>
       </c>
@@ -2256,18 +2159,8 @@
       <c r="AV11" s="2">
         <v>8.7750658392906189E-2</v>
       </c>
-      <c r="AW11" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX11" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA11">
-        <f t="shared" si="0"/>
-        <v>20.140974774851099</v>
-      </c>
     </row>
-    <row r="12" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>35370</v>
       </c>
@@ -2412,18 +2305,8 @@
       <c r="AV12" s="2">
         <v>4.0709704160690308E-2</v>
       </c>
-      <c r="AW12" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX12" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA12">
-        <f t="shared" si="0"/>
-        <v>33.930950973558687</v>
-      </c>
     </row>
-    <row r="13" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>35400</v>
       </c>
@@ -2568,18 +2451,8 @@
       <c r="AV13" s="2">
         <v>6.4257636666297913E-2</v>
       </c>
-      <c r="AW13" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX13" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA13">
-        <f t="shared" si="0"/>
-        <v>40.477710589804303</v>
-      </c>
     </row>
-    <row r="14" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>35431</v>
       </c>
@@ -2724,18 +2597,8 @@
       <c r="AV14" s="2">
         <v>7.1649447083473206E-2</v>
       </c>
-      <c r="AW14" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX14" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA14">
-        <f t="shared" si="0"/>
-        <v>17.765279848909994</v>
-      </c>
     </row>
-    <row r="15" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>35462</v>
       </c>
@@ -2880,18 +2743,8 @@
       <c r="AV15" s="2">
         <v>9.1797016561031342E-2</v>
       </c>
-      <c r="AW15" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX15" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA15">
-        <f t="shared" si="0"/>
-        <v>37.168849624693699</v>
-      </c>
     </row>
-    <row r="16" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>35490</v>
       </c>
@@ -3036,18 +2889,8 @@
       <c r="AV16" s="2">
         <v>8.5084103047847748E-2</v>
       </c>
-      <c r="AW16" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX16" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA16">
-        <f t="shared" si="0"/>
-        <v>34.246073266477325</v>
-      </c>
     </row>
-    <row r="17" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>35521</v>
       </c>
@@ -3192,18 +3035,8 @@
       <c r="AV17" s="2">
         <v>0.11464796215295792</v>
       </c>
-      <c r="AW17" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX17" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA17">
-        <f t="shared" si="0"/>
-        <v>49.186503416658574</v>
-      </c>
     </row>
-    <row r="18" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>35551</v>
       </c>
@@ -3348,18 +3181,8 @@
       <c r="AV18" s="2">
         <v>0.12738020718097687</v>
       </c>
-      <c r="AW18" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX18" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA18">
-        <f t="shared" si="0"/>
-        <v>35.825647466363328</v>
-      </c>
     </row>
-    <row r="19" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>35582</v>
       </c>
@@ -3504,18 +3327,8 @@
       <c r="AV19" s="2">
         <v>3.7558045238256454E-2</v>
       </c>
-      <c r="AW19" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX19" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA19">
-        <f t="shared" si="0"/>
-        <v>33.091155331769109</v>
-      </c>
     </row>
-    <row r="20" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>35612</v>
       </c>
@@ -3660,18 +3473,8 @@
       <c r="AV20" s="2">
         <v>3.3982396125793457E-2</v>
       </c>
-      <c r="AW20" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX20" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA20">
-        <f t="shared" si="0"/>
-        <v>32.869970896079074</v>
-      </c>
     </row>
-    <row r="21" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>35643</v>
       </c>
@@ -3816,18 +3619,8 @@
       <c r="AV21" s="2">
         <v>6.5919578075408936E-2</v>
       </c>
-      <c r="AW21" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX21" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA21">
-        <f t="shared" si="0"/>
-        <v>24.809081225092942</v>
-      </c>
     </row>
-    <row r="22" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>35674</v>
       </c>
@@ -3972,18 +3765,8 @@
       <c r="AV22" s="2">
         <v>5.2529629319906235E-2</v>
       </c>
-      <c r="AW22" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX22" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA22">
-        <f t="shared" si="0"/>
-        <v>27.523532073498373</v>
-      </c>
     </row>
-    <row r="23" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>35704</v>
       </c>
@@ -4128,18 +3911,8 @@
       <c r="AV23" s="2">
         <v>6.6991470754146576E-2</v>
       </c>
-      <c r="AW23" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX23" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA23">
-        <f t="shared" si="0"/>
-        <v>51.488072893704071</v>
-      </c>
     </row>
-    <row r="24" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>35735</v>
       </c>
@@ -4284,18 +4057,8 @@
       <c r="AV24" s="2">
         <v>2.312367781996727E-2</v>
       </c>
-      <c r="AW24" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX24" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA24">
-        <f t="shared" si="0"/>
-        <v>75.149585574032841</v>
-      </c>
     </row>
-    <row r="25" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>35765</v>
       </c>
@@ -4440,18 +4203,8 @@
       <c r="AV25" s="2">
         <v>5.9090014547109604E-2</v>
       </c>
-      <c r="AW25" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX25" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA25">
-        <f t="shared" si="0"/>
-        <v>27.401487853226381</v>
-      </c>
     </row>
-    <row r="26" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>35796</v>
       </c>
@@ -4596,18 +4349,8 @@
       <c r="AV26" s="2">
         <v>3.0685201287269592E-2</v>
       </c>
-      <c r="AW26" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX26" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA26">
-        <f t="shared" si="0"/>
-        <v>42.958092546439353</v>
-      </c>
     </row>
-    <row r="27" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>35827</v>
       </c>
@@ -4752,18 +4495,8 @@
       <c r="AV27" s="2">
         <v>3.8576524704694748E-2</v>
       </c>
-      <c r="AW27" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX27" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA27">
-        <f t="shared" si="0"/>
-        <v>54.026754921976938</v>
-      </c>
     </row>
-    <row r="28" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>35855</v>
       </c>
@@ -4908,18 +4641,8 @@
       <c r="AV28" s="2">
         <v>5.5484171956777573E-2</v>
       </c>
-      <c r="AW28" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX28" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA28">
-        <f t="shared" si="0"/>
-        <v>30.437441754722844</v>
-      </c>
     </row>
-    <row r="29" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>35886</v>
       </c>
@@ -5064,18 +4787,8 @@
       <c r="AV29" s="2">
         <v>3.1026029959321022E-2</v>
       </c>
-      <c r="AW29" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX29" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA29">
-        <f t="shared" si="0"/>
-        <v>31.17648783110689</v>
-      </c>
     </row>
-    <row r="30" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>35916</v>
       </c>
@@ -5220,18 +4933,8 @@
       <c r="AV30" s="2">
         <v>0.10360082983970642</v>
       </c>
-      <c r="AW30" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX30" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA30">
-        <f t="shared" si="0"/>
-        <v>139.89377694975806</v>
-      </c>
     </row>
-    <row r="31" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>35947</v>
       </c>
@@ -5376,18 +5079,8 @@
       <c r="AV31" s="2">
         <v>8.7704405188560486E-2</v>
       </c>
-      <c r="AW31" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX31" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA31">
-        <f t="shared" si="0"/>
-        <v>92.687201867376785</v>
-      </c>
     </row>
-    <row r="32" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>35977</v>
       </c>
@@ -5532,18 +5225,8 @@
       <c r="AV32" s="2">
         <v>6.5923526883125305E-2</v>
       </c>
-      <c r="AW32" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX32" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA32">
-        <f t="shared" si="0"/>
-        <v>57.516736282927639</v>
-      </c>
     </row>
-    <row r="33" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>36008</v>
       </c>
@@ -5688,18 +5371,8 @@
       <c r="AV33" s="2">
         <v>0.22671511769294739</v>
       </c>
-      <c r="AW33" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX33" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA33">
-        <f t="shared" si="0"/>
-        <v>46.425961301560619</v>
-      </c>
     </row>
-    <row r="34" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>36039</v>
       </c>
@@ -5844,18 +5517,8 @@
       <c r="AV34" s="2">
         <v>0.11955792456865311</v>
       </c>
-      <c r="AW34" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX34" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA34">
-        <f t="shared" si="0"/>
-        <v>32.255527178537804</v>
-      </c>
     </row>
-    <row r="35" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>36069</v>
       </c>
@@ -6000,18 +5663,8 @@
       <c r="AV35" s="2">
         <v>7.6489418745040894E-2</v>
       </c>
-      <c r="AW35" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX35" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA35">
-        <f t="shared" si="0"/>
-        <v>26.803611771556785</v>
-      </c>
     </row>
-    <row r="36" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>36100</v>
       </c>
@@ -6156,18 +5809,8 @@
       <c r="AV36" s="2">
         <v>7.1738153696060181E-2</v>
       </c>
-      <c r="AW36" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX36" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA36">
-        <f t="shared" si="0"/>
-        <v>47.550955788901554</v>
-      </c>
     </row>
-    <row r="37" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>36130</v>
       </c>
@@ -6312,18 +5955,8 @@
       <c r="AV37" s="2">
         <v>9.1638751327991486E-2</v>
       </c>
-      <c r="AW37" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX37" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA37">
-        <f t="shared" si="0"/>
-        <v>57.90853090999839</v>
-      </c>
     </row>
-    <row r="38" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>36161</v>
       </c>
@@ -6468,18 +6101,8 @@
       <c r="AV38" s="2">
         <v>7.5918614864349365E-2</v>
       </c>
-      <c r="AW38" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX38" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA38">
-        <f t="shared" si="0"/>
-        <v>40.75697754412689</v>
-      </c>
     </row>
-    <row r="39" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>36192</v>
       </c>
@@ -6624,18 +6247,8 @@
       <c r="AV39" s="2">
         <v>3.743278980255127E-2</v>
       </c>
-      <c r="AW39" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX39" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA39">
-        <f t="shared" si="0"/>
-        <v>39.667426683705642</v>
-      </c>
     </row>
-    <row r="40" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>36220</v>
       </c>
@@ -6780,18 +6393,8 @@
       <c r="AV40" s="2">
         <v>4.7307886183261871E-2</v>
       </c>
-      <c r="AW40" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX40" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA40">
-        <f t="shared" si="0"/>
-        <v>74.449304524618299</v>
-      </c>
     </row>
-    <row r="41" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>36251</v>
       </c>
@@ -6936,18 +6539,8 @@
       <c r="AV41" s="2">
         <v>3.7218533456325531E-2</v>
       </c>
-      <c r="AW41" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX41" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA41">
-        <f t="shared" si="0"/>
-        <v>72.651077220273081</v>
-      </c>
     </row>
-    <row r="42" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>36281</v>
       </c>
@@ -7092,18 +6685,8 @@
       <c r="AV42" s="2">
         <v>3.9286792278289795E-2</v>
       </c>
-      <c r="AW42" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX42" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA42">
-        <f t="shared" si="0"/>
-        <v>128.88254607037638</v>
-      </c>
     </row>
-    <row r="43" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>36312</v>
       </c>
@@ -7248,18 +6831,8 @@
       <c r="AV43" s="2">
         <v>5.5106539279222488E-2</v>
       </c>
-      <c r="AW43" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX43" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA43">
-        <f t="shared" si="0"/>
-        <v>91.371754432233828</v>
-      </c>
     </row>
-    <row r="44" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>36342</v>
       </c>
@@ -7404,18 +6977,8 @@
       <c r="AV44" s="2">
         <v>5.0546534359455109E-2</v>
       </c>
-      <c r="AW44" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX44" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA44">
-        <f t="shared" si="0"/>
-        <v>56.447221943343187</v>
-      </c>
     </row>
-    <row r="45" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>36373</v>
       </c>
@@ -7560,18 +7123,8 @@
       <c r="AV45" s="2">
         <v>6.5464302897453308E-2</v>
       </c>
-      <c r="AW45" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX45" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA45">
-        <f t="shared" si="0"/>
-        <v>58.404160890965983</v>
-      </c>
     </row>
-    <row r="46" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>36404</v>
       </c>
@@ -7716,18 +7269,8 @@
       <c r="AV46" s="2">
         <v>5.0517808645963669E-2</v>
       </c>
-      <c r="AW46" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX46" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA46">
-        <f t="shared" si="0"/>
-        <v>55.169761957043441</v>
-      </c>
     </row>
-    <row r="47" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>36434</v>
       </c>
@@ -7872,18 +7415,8 @@
       <c r="AV47" s="2">
         <v>0.11800598353147507</v>
       </c>
-      <c r="AW47" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX47" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA47">
-        <f t="shared" si="0"/>
-        <v>65.633526524013547</v>
-      </c>
     </row>
-    <row r="48" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>36465</v>
       </c>
@@ -8028,18 +7561,8 @@
       <c r="AV48" s="2">
         <v>8.6629226803779602E-2</v>
       </c>
-      <c r="AW48" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX48" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA48">
-        <f t="shared" si="0"/>
-        <v>53.610733607835549</v>
-      </c>
     </row>
-    <row r="49" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>36495</v>
       </c>
@@ -8184,18 +7707,8 @@
       <c r="AV49" s="2">
         <v>7.3046021163463593E-2</v>
       </c>
-      <c r="AW49" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX49" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA49">
-        <f t="shared" si="0"/>
-        <v>71.140129055342683</v>
-      </c>
     </row>
-    <row r="50" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>36526</v>
       </c>
@@ -8340,18 +7853,8 @@
       <c r="AV50" s="2">
         <v>6.5943285822868347E-2</v>
       </c>
-      <c r="AW50" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX50" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA50">
-        <f t="shared" si="0"/>
-        <v>45.923509921168204</v>
-      </c>
     </row>
-    <row r="51" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>36557</v>
       </c>
@@ -8496,18 +7999,8 @@
       <c r="AV51" s="2">
         <v>6.3730992376804352E-2</v>
       </c>
-      <c r="AW51" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX51" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA51">
-        <f t="shared" si="0"/>
-        <v>35.984529197136666</v>
-      </c>
     </row>
-    <row r="52" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>36586</v>
       </c>
@@ -8652,18 +8145,8 @@
       <c r="AV52" s="2">
         <v>9.5803797245025635E-2</v>
       </c>
-      <c r="AW52" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX52" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA52">
-        <f t="shared" si="0"/>
-        <v>47.409645716985438</v>
-      </c>
     </row>
-    <row r="53" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>36617</v>
       </c>
@@ -8808,18 +8291,8 @@
       <c r="AV53" s="2">
         <v>8.9949630200862885E-2</v>
       </c>
-      <c r="AW53" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX53" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA53">
-        <f t="shared" si="0"/>
-        <v>35.417029175770878</v>
-      </c>
     </row>
-    <row r="54" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>36647</v>
       </c>
@@ -8964,18 +8437,8 @@
       <c r="AV54" s="2">
         <v>0.19322024285793304</v>
       </c>
-      <c r="AW54" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX54" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA54">
-        <f t="shared" si="0"/>
-        <v>52.424436209365389</v>
-      </c>
     </row>
-    <row r="55" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>36678</v>
       </c>
@@ -9120,18 +8583,8 @@
       <c r="AV55" s="2">
         <v>5.1534585654735565E-2</v>
       </c>
-      <c r="AW55" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX55" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA55">
-        <f t="shared" si="0"/>
-        <v>57.134611809100747</v>
-      </c>
     </row>
-    <row r="56" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>36708</v>
       </c>
@@ -9276,18 +8729,8 @@
       <c r="AV56" s="2">
         <v>7.709871232509613E-2</v>
       </c>
-      <c r="AW56" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX56" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA56">
-        <f t="shared" si="0"/>
-        <v>57.072308424447563</v>
-      </c>
     </row>
-    <row r="57" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>36739</v>
       </c>
@@ -9432,18 +8875,8 @@
       <c r="AV57" s="2">
         <v>9.1781146824359894E-2</v>
       </c>
-      <c r="AW57" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX57" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA57">
-        <f t="shared" si="0"/>
-        <v>31.724050696607474</v>
-      </c>
     </row>
-    <row r="58" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>36770</v>
       </c>
@@ -9588,18 +9021,8 @@
       <c r="AV58" s="2">
         <v>6.1536740511655807E-2</v>
       </c>
-      <c r="AW58" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX58" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA58">
-        <f t="shared" si="0"/>
-        <v>47.466163369476249</v>
-      </c>
     </row>
-    <row r="59" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>36800</v>
       </c>
@@ -9744,18 +9167,8 @@
       <c r="AV59" s="2">
         <v>4.39947210252285E-2</v>
       </c>
-      <c r="AW59" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX59" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA59">
-        <f t="shared" si="0"/>
-        <v>30.742343304670904</v>
-      </c>
     </row>
-    <row r="60" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>36831</v>
       </c>
@@ -9900,18 +9313,8 @@
       <c r="AV60" s="2">
         <v>3.3371340483427048E-2</v>
       </c>
-      <c r="AW60" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX60" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA60">
-        <f t="shared" si="0"/>
-        <v>27.26013743570569</v>
-      </c>
     </row>
-    <row r="61" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>36861</v>
       </c>
@@ -10056,18 +9459,8 @@
       <c r="AV61" s="2">
         <v>6.1749357730150223E-2</v>
       </c>
-      <c r="AW61" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX61" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA61">
-        <f t="shared" si="0"/>
-        <v>29.670591333875407</v>
-      </c>
     </row>
-    <row r="62" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>36892</v>
       </c>
@@ -10212,18 +9605,8 @@
       <c r="AV62" s="2">
         <v>4.3416596949100494E-2</v>
       </c>
-      <c r="AW62" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX62" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA62">
-        <f t="shared" si="0"/>
-        <v>43.328753916576794</v>
-      </c>
     </row>
-    <row r="63" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>36923</v>
       </c>
@@ -10368,18 +9751,8 @@
       <c r="AV63" s="2">
         <v>2.5274066254496574E-2</v>
       </c>
-      <c r="AW63" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX63" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA63">
-        <f t="shared" si="0"/>
-        <v>52.506285216893865</v>
-      </c>
     </row>
-    <row r="64" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>36951</v>
       </c>
@@ -10524,18 +9897,8 @@
       <c r="AV64" s="2">
         <v>3.2856009900569916E-2</v>
       </c>
-      <c r="AW64" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX64" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA64">
-        <f t="shared" si="0"/>
-        <v>43.137382821831444</v>
-      </c>
     </row>
-    <row r="65" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>36982</v>
       </c>
@@ -10680,18 +10043,8 @@
       <c r="AV65" s="2">
         <v>2.1107861772179604E-2</v>
       </c>
-      <c r="AW65" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX65" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA65">
-        <f t="shared" si="0"/>
-        <v>67.088957536355977</v>
-      </c>
     </row>
-    <row r="66" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>37012</v>
       </c>
@@ -10836,18 +10189,8 @@
       <c r="AV66" s="2">
         <v>3.4168563783168793E-2</v>
       </c>
-      <c r="AW66" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX66" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA66">
-        <f t="shared" si="0"/>
-        <v>55.66689550133227</v>
-      </c>
     </row>
-    <row r="67" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>37043</v>
       </c>
@@ -10992,18 +10335,8 @@
       <c r="AV67" s="2">
         <v>3.8704298436641693E-2</v>
       </c>
-      <c r="AW67" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX67" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA67">
-        <f t="shared" ref="BA67:BA130" si="1">(L67/AVERAGE(L67:L423))*100</f>
-        <v>47.686328384106716</v>
-      </c>
     </row>
-    <row r="68" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>37073</v>
       </c>
@@ -11148,18 +10481,8 @@
       <c r="AV68" s="2">
         <v>5.0186630338430405E-2</v>
       </c>
-      <c r="AW68" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX68" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA68">
-        <f t="shared" si="1"/>
-        <v>51.716602224426723</v>
-      </c>
     </row>
-    <row r="69" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>37104</v>
       </c>
@@ -11304,18 +10627,8 @@
       <c r="AV69" s="2">
         <v>6.8561457097530365E-2</v>
       </c>
-      <c r="AW69" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX69" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA69">
-        <f t="shared" si="1"/>
-        <v>36.271012103199759</v>
-      </c>
     </row>
-    <row r="70" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>37135</v>
       </c>
@@ -11460,18 +10773,8 @@
       <c r="AV70" s="2">
         <v>0.13241046667098999</v>
       </c>
-      <c r="AW70" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX70" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA70">
-        <f t="shared" si="1"/>
-        <v>127.80776823154913</v>
-      </c>
     </row>
-    <row r="71" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>37165</v>
       </c>
@@ -11616,18 +10919,8 @@
       <c r="AV71" s="2">
         <v>0.12962299585342407</v>
       </c>
-      <c r="AW71" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX71" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA71">
-        <f t="shared" si="1"/>
-        <v>109.45843430942182</v>
-      </c>
     </row>
-    <row r="72" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>37196</v>
       </c>
@@ -11772,18 +11065,8 @@
       <c r="AV72" s="2">
         <v>0.13377925753593445</v>
       </c>
-      <c r="AW72" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX72" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA72">
-        <f t="shared" si="1"/>
-        <v>59.90498902682392</v>
-      </c>
     </row>
-    <row r="73" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>37226</v>
       </c>
@@ -11928,18 +11211,8 @@
       <c r="AV73" s="2">
         <v>7.9782992601394653E-2</v>
       </c>
-      <c r="AW73" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX73" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA73">
-        <f t="shared" si="1"/>
-        <v>64.585055539510066</v>
-      </c>
     </row>
-    <row r="74" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>37257</v>
       </c>
@@ -12084,18 +11357,8 @@
       <c r="AV74" s="2">
         <v>6.3942514359951019E-2</v>
       </c>
-      <c r="AW74" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX74" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA74">
-        <f t="shared" si="1"/>
-        <v>56.500329579102548</v>
-      </c>
     </row>
-    <row r="75" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>37288</v>
       </c>
@@ -12240,18 +11503,8 @@
       <c r="AV75" s="2">
         <v>9.7297638654708862E-2</v>
       </c>
-      <c r="AW75" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX75" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA75">
-        <f t="shared" si="1"/>
-        <v>61.785337407398025</v>
-      </c>
     </row>
-    <row r="76" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>37316</v>
       </c>
@@ -12396,18 +11649,8 @@
       <c r="AV76" s="2">
         <v>9.8465099930763245E-2</v>
       </c>
-      <c r="AW76" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX76" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA76">
-        <f t="shared" si="1"/>
-        <v>46.885799936650834</v>
-      </c>
     </row>
-    <row r="77" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>37347</v>
       </c>
@@ -12552,18 +11795,8 @@
       <c r="AV77" s="2">
         <v>6.4417175948619843E-2</v>
       </c>
-      <c r="AW77" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX77" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA77">
-        <f t="shared" si="1"/>
-        <v>27.818884788544469</v>
-      </c>
     </row>
-    <row r="78" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>37377</v>
       </c>
@@ -12708,18 +11941,8 @@
       <c r="AV78" s="2">
         <v>5.0593733787536621E-2</v>
       </c>
-      <c r="AW78" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX78" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA78">
-        <f t="shared" si="1"/>
-        <v>45.52093818124861</v>
-      </c>
     </row>
-    <row r="79" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>37408</v>
       </c>
@@ -12864,18 +12087,8 @@
       <c r="AV79" s="2">
         <v>0.10179530084133148</v>
       </c>
-      <c r="AW79" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX79" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA79">
-        <f t="shared" si="1"/>
-        <v>36.96348722778496</v>
-      </c>
     </row>
-    <row r="80" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>37438</v>
       </c>
@@ -13020,18 +12233,8 @@
       <c r="AV80" s="2">
         <v>6.3329219818115234E-2</v>
       </c>
-      <c r="AW80" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX80" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA80">
-        <f t="shared" si="1"/>
-        <v>29.041450437085466</v>
-      </c>
     </row>
-    <row r="81" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>37469</v>
       </c>
@@ -13176,18 +12379,8 @@
       <c r="AV81" s="2">
         <v>0.10003872215747833</v>
       </c>
-      <c r="AW81" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX81" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA81">
-        <f t="shared" si="1"/>
-        <v>42.1740696076955</v>
-      </c>
     </row>
-    <row r="82" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>37500</v>
       </c>
@@ -13332,18 +12525,8 @@
       <c r="AV82" s="2">
         <v>0.17814362049102783</v>
       </c>
-      <c r="AW82" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX82" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA82">
-        <f t="shared" si="1"/>
-        <v>83.11774124799561</v>
-      </c>
     </row>
-    <row r="83" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>37530</v>
       </c>
@@ -13488,18 +12671,8 @@
       <c r="AV83" s="2">
         <v>8.1280305981636047E-2</v>
       </c>
-      <c r="AW83" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX83" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA83">
-        <f t="shared" si="1"/>
-        <v>96.805716966356272</v>
-      </c>
     </row>
-    <row r="84" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>37561</v>
       </c>
@@ -13644,18 +12817,8 @@
       <c r="AV84" s="2">
         <v>4.7139238566160202E-2</v>
       </c>
-      <c r="AW84" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX84" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA84">
-        <f t="shared" si="1"/>
-        <v>59.033025355431946</v>
-      </c>
     </row>
-    <row r="85" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <v>37591</v>
       </c>
@@ -13800,18 +12963,8 @@
       <c r="AV85" s="2">
         <v>8.3245284855365753E-2</v>
       </c>
-      <c r="AW85" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX85" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA85">
-        <f t="shared" si="1"/>
-        <v>78.639680931865641</v>
-      </c>
     </row>
-    <row r="86" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>37622</v>
       </c>
@@ -13956,18 +13109,8 @@
       <c r="AV86" s="2">
         <v>0.10121156275272369</v>
       </c>
-      <c r="AW86" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX86" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA86">
-        <f t="shared" si="1"/>
-        <v>133.05241202438322</v>
-      </c>
     </row>
-    <row r="87" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>37653</v>
       </c>
@@ -14112,18 +13255,8 @@
       <c r="AV87" s="2">
         <v>0.10850486904382706</v>
       </c>
-      <c r="AW87" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX87" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA87">
-        <f t="shared" si="1"/>
-        <v>153.7194837840662</v>
-      </c>
     </row>
-    <row r="88" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>37681</v>
       </c>
@@ -14268,18 +13401,8 @@
       <c r="AV88" s="2">
         <v>9.4232425093650818E-2</v>
       </c>
-      <c r="AW88" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX88" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA88">
-        <f t="shared" si="1"/>
-        <v>131.50524270962697</v>
-      </c>
     </row>
-    <row r="89" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
         <v>37712</v>
       </c>
@@ -14424,18 +13547,8 @@
       <c r="AV89" s="2">
         <v>8.1613615155220032E-2</v>
       </c>
-      <c r="AW89" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX89" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA89">
-        <f t="shared" si="1"/>
-        <v>145.12429935677542</v>
-      </c>
     </row>
-    <row r="90" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>37742</v>
       </c>
@@ -14580,18 +13693,8 @@
       <c r="AV90" s="2">
         <v>7.7094398438930511E-2</v>
       </c>
-      <c r="AW90" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX90" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA90">
-        <f t="shared" si="1"/>
-        <v>76.10470244689995</v>
-      </c>
     </row>
-    <row r="91" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
         <v>37773</v>
       </c>
@@ -14736,18 +13839,8 @@
       <c r="AV91" s="2">
         <v>5.4238107055425644E-2</v>
       </c>
-      <c r="AW91" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX91" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA91">
-        <f t="shared" si="1"/>
-        <v>73.841588303669099</v>
-      </c>
     </row>
-    <row r="92" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>37803</v>
       </c>
@@ -14892,18 +13985,8 @@
       <c r="AV92" s="2">
         <v>0.13190588355064392</v>
       </c>
-      <c r="AW92" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX92" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA92">
-        <f t="shared" si="1"/>
-        <v>63.083935438055519</v>
-      </c>
     </row>
-    <row r="93" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
         <v>37834</v>
       </c>
@@ -15048,18 +14131,8 @@
       <c r="AV93" s="2">
         <v>7.1484073996543884E-2</v>
       </c>
-      <c r="AW93" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX93" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA93">
-        <f t="shared" si="1"/>
-        <v>65.852912135456108</v>
-      </c>
     </row>
-    <row r="94" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
         <v>37865</v>
       </c>
@@ -15204,18 +14277,8 @@
       <c r="AV94" s="2">
         <v>3.824654221534729E-2</v>
       </c>
-      <c r="AW94" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX94" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA94">
-        <f t="shared" si="1"/>
-        <v>48.368337957313251</v>
-      </c>
     </row>
-    <row r="95" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <v>37895</v>
       </c>
@@ -15360,18 +14423,8 @@
       <c r="AV95" s="2">
         <v>2.9657589271664619E-2</v>
       </c>
-      <c r="AW95" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX95" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA95">
-        <f t="shared" si="1"/>
-        <v>57.379511943842608</v>
-      </c>
     </row>
-    <row r="96" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <v>37926</v>
       </c>
@@ -15516,18 +14569,8 @@
       <c r="AV96" s="2">
         <v>2.7083145454525948E-2</v>
       </c>
-      <c r="AW96" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX96" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA96">
-        <f t="shared" si="1"/>
-        <v>46.368107205266568</v>
-      </c>
     </row>
-    <row r="97" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
         <v>37956</v>
       </c>
@@ -15672,18 +14715,8 @@
       <c r="AV97" s="2">
         <v>4.7782875597476959E-2</v>
       </c>
-      <c r="AW97" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX97" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA97">
-        <f t="shared" si="1"/>
-        <v>75.280922956965114</v>
-      </c>
     </row>
-    <row r="98" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
         <v>37987</v>
       </c>
@@ -15828,18 +14861,8 @@
       <c r="AV98" s="2">
         <v>4.7724153846502304E-2</v>
       </c>
-      <c r="AW98" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX98" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA98">
-        <f t="shared" si="1"/>
-        <v>58.846146542319076</v>
-      </c>
     </row>
-    <row r="99" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
         <v>38018</v>
       </c>
@@ -15984,18 +15007,8 @@
       <c r="AV99" s="2">
         <v>3.6981109529733658E-2</v>
       </c>
-      <c r="AW99" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX99" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA99">
-        <f t="shared" si="1"/>
-        <v>62.693468853696388</v>
-      </c>
     </row>
-    <row r="100" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
         <v>38047</v>
       </c>
@@ -16140,18 +15153,8 @@
       <c r="AV100" s="2">
         <v>6.8632215261459351E-2</v>
       </c>
-      <c r="AW100" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX100" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA100">
-        <f t="shared" si="1"/>
-        <v>52.098258277806899</v>
-      </c>
     </row>
-    <row r="101" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
         <v>38078</v>
       </c>
@@ -16296,18 +15299,8 @@
       <c r="AV101" s="2">
         <v>5.0661582499742508E-2</v>
       </c>
-      <c r="AW101" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX101" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA101">
-        <f t="shared" si="1"/>
-        <v>71.935529855252412</v>
-      </c>
     </row>
-    <row r="102" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
         <v>38108</v>
       </c>
@@ -16452,18 +15445,8 @@
       <c r="AV102" s="2">
         <v>7.0410139858722687E-2</v>
       </c>
-      <c r="AW102" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX102" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA102">
-        <f t="shared" si="1"/>
-        <v>66.966974537105344</v>
-      </c>
     </row>
-    <row r="103" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
         <v>38139</v>
       </c>
@@ -16608,18 +15591,8 @@
       <c r="AV103" s="2">
         <v>4.7758344560861588E-2</v>
       </c>
-      <c r="AW103" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX103" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA103">
-        <f t="shared" si="1"/>
-        <v>71.880135655843929</v>
-      </c>
     </row>
-    <row r="104" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
         <v>38169</v>
       </c>
@@ -16764,18 +15737,8 @@
       <c r="AV104" s="2">
         <v>4.8255272209644318E-2</v>
       </c>
-      <c r="AW104" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX104" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA104">
-        <f t="shared" si="1"/>
-        <v>49.332672899614842</v>
-      </c>
     </row>
-    <row r="105" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
         <v>38200</v>
       </c>
@@ -16920,18 +15883,8 @@
       <c r="AV105" s="2">
         <v>0.10639268159866333</v>
       </c>
-      <c r="AW105" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX105" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA105">
-        <f t="shared" si="1"/>
-        <v>42.325999196283689</v>
-      </c>
     </row>
-    <row r="106" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
         <v>38231</v>
       </c>
@@ -17076,18 +16029,8 @@
       <c r="AV106" s="2">
         <v>4.7856908291578293E-2</v>
       </c>
-      <c r="AW106" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX106" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA106">
-        <f t="shared" si="1"/>
-        <v>67.821650275660986</v>
-      </c>
     </row>
-    <row r="107" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
         <v>38261</v>
       </c>
@@ -17232,18 +16175,8 @@
       <c r="AV107" s="2">
         <v>4.0073275566101074E-2</v>
       </c>
-      <c r="AW107" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX107" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA107">
-        <f t="shared" si="1"/>
-        <v>52.952437236245217</v>
-      </c>
     </row>
-    <row r="108" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
         <v>38292</v>
       </c>
@@ -17388,18 +16321,8 @@
       <c r="AV108" s="2">
         <v>0.12308246642351151</v>
       </c>
-      <c r="AW108" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX108" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA108">
-        <f t="shared" si="1"/>
-        <v>57.820995224602314</v>
-      </c>
     </row>
-    <row r="109" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
         <v>38322</v>
       </c>
@@ -17544,18 +16467,8 @@
       <c r="AV109" s="2">
         <v>7.621224969625473E-2</v>
       </c>
-      <c r="AW109" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX109" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA109">
-        <f t="shared" si="1"/>
-        <v>65.096706296437944</v>
-      </c>
     </row>
-    <row r="110" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
         <v>38353</v>
       </c>
@@ -17700,18 +16613,8 @@
       <c r="AV110" s="2">
         <v>3.0169552192091942E-2</v>
       </c>
-      <c r="AW110" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX110" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA110">
-        <f t="shared" si="1"/>
-        <v>71.813740028514317</v>
-      </c>
     </row>
-    <row r="111" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
         <v>38384</v>
       </c>
@@ -17856,18 +16759,8 @@
       <c r="AV111" s="2">
         <v>4.1823506355285645E-2</v>
       </c>
-      <c r="AW111" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX111" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA111">
-        <f t="shared" si="1"/>
-        <v>99.441072998928504</v>
-      </c>
     </row>
-    <row r="112" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
         <v>38412</v>
       </c>
@@ -18012,18 +16905,8 @@
       <c r="AV112" s="2">
         <v>5.1543440669775009E-2</v>
       </c>
-      <c r="AW112" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX112" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA112">
-        <f t="shared" si="1"/>
-        <v>83.968596391475401</v>
-      </c>
     </row>
-    <row r="113" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
         <v>38443</v>
       </c>
@@ -18168,18 +17051,8 @@
       <c r="AV113" s="2">
         <v>7.9460844397544861E-2</v>
       </c>
-      <c r="AW113" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX113" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA113">
-        <f t="shared" si="1"/>
-        <v>57.805936581885135</v>
-      </c>
     </row>
-    <row r="114" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
         <v>38473</v>
       </c>
@@ -18324,18 +17197,8 @@
       <c r="AV114" s="2">
         <v>2.3923445492982864E-2</v>
       </c>
-      <c r="AW114" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX114" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA114">
-        <f t="shared" si="1"/>
-        <v>65.25696473296081</v>
-      </c>
     </row>
-    <row r="115" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
         <v>38504</v>
       </c>
@@ -18480,18 +17343,8 @@
       <c r="AV115" s="2">
         <v>4.2159784585237503E-2</v>
       </c>
-      <c r="AW115" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX115" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA115">
-        <f t="shared" si="1"/>
-        <v>61.34175140679784</v>
-      </c>
     </row>
-    <row r="116" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
         <v>38534</v>
       </c>
@@ -18636,18 +17489,8 @@
       <c r="AV116" s="2">
         <v>7.93723464012146E-2</v>
       </c>
-      <c r="AW116" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX116" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA116">
-        <f t="shared" si="1"/>
-        <v>114.06435976671683</v>
-      </c>
     </row>
-    <row r="117" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
         <v>38565</v>
       </c>
@@ -18792,18 +17635,8 @@
       <c r="AV117" s="2">
         <v>4.8553116619586945E-2</v>
       </c>
-      <c r="AW117" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX117" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA117">
-        <f t="shared" si="1"/>
-        <v>62.293666460226163</v>
-      </c>
     </row>
-    <row r="118" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
         <v>38596</v>
       </c>
@@ -18948,18 +17781,8 @@
       <c r="AV118" s="2">
         <v>5.2574701607227325E-2</v>
       </c>
-      <c r="AW118" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX118" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA118">
-        <f t="shared" si="1"/>
-        <v>78.66465882260627</v>
-      </c>
     </row>
-    <row r="119" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
         <v>38626</v>
       </c>
@@ -19104,18 +17927,8 @@
       <c r="AV119" s="2">
         <v>4.3091066181659698E-2</v>
       </c>
-      <c r="AW119" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX119" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA119">
-        <f t="shared" si="1"/>
-        <v>38.876554708693753</v>
-      </c>
     </row>
-    <row r="120" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
         <v>38657</v>
       </c>
@@ -19260,18 +18073,8 @@
       <c r="AV120" s="2">
         <v>3.049803338944912E-2</v>
       </c>
-      <c r="AW120" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX120" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA120">
-        <f t="shared" si="1"/>
-        <v>61.272536140822055</v>
-      </c>
     </row>
-    <row r="121" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
         <v>38687</v>
       </c>
@@ -19416,18 +18219,8 @@
       <c r="AV121" s="2">
         <v>2.1951142698526382E-2</v>
       </c>
-      <c r="AW121" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX121" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA121">
-        <f t="shared" si="1"/>
-        <v>33.415345904645726</v>
-      </c>
     </row>
-    <row r="122" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
         <v>38718</v>
       </c>
@@ -19572,18 +18365,8 @@
       <c r="AV122" s="2">
         <v>5.232379212975502E-2</v>
       </c>
-      <c r="AW122" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX122" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA122">
-        <f t="shared" si="1"/>
-        <v>98.596996870466</v>
-      </c>
     </row>
-    <row r="123" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
         <v>38749</v>
       </c>
@@ -19728,18 +18511,8 @@
       <c r="AV123" s="2">
         <v>5.0944056361913681E-2</v>
       </c>
-      <c r="AW123" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX123" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA123">
-        <f t="shared" si="1"/>
-        <v>73.632403635257077</v>
-      </c>
     </row>
-    <row r="124" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
         <v>38777</v>
       </c>
@@ -19884,18 +18657,8 @@
       <c r="AV124" s="2">
         <v>3.730272501707077E-2</v>
       </c>
-      <c r="AW124" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX124" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA124">
-        <f t="shared" si="1"/>
-        <v>82.406551404098707</v>
-      </c>
     </row>
-    <row r="125" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
         <v>38808</v>
       </c>
@@ -20040,18 +18803,8 @@
       <c r="AV125" s="2">
         <v>2.8203440830111504E-2</v>
       </c>
-      <c r="AW125" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX125" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA125">
-        <f t="shared" si="1"/>
-        <v>84.063663992581297</v>
-      </c>
     </row>
-    <row r="126" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
         <v>38838</v>
       </c>
@@ -20196,18 +18949,8 @@
       <c r="AV126" s="2">
         <v>4.1897352784872055E-2</v>
       </c>
-      <c r="AW126" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX126" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA126">
-        <f t="shared" si="1"/>
-        <v>88.620763334052839</v>
-      </c>
     </row>
-    <row r="127" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
         <v>38869</v>
       </c>
@@ -20352,18 +19095,8 @@
       <c r="AV127" s="2">
         <v>6.0443047434091568E-2</v>
       </c>
-      <c r="AW127" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX127" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA127">
-        <f t="shared" si="1"/>
-        <v>84.271313682450796</v>
-      </c>
     </row>
-    <row r="128" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
         <v>38899</v>
       </c>
@@ -20508,18 +19241,8 @@
       <c r="AV128" s="2">
         <v>4.129081591963768E-2</v>
       </c>
-      <c r="AW128" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX128" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA128">
-        <f t="shared" si="1"/>
-        <v>115.70196091214642</v>
-      </c>
     </row>
-    <row r="129" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
         <v>38930</v>
       </c>
@@ -20664,18 +19387,8 @@
       <c r="AV129" s="2">
         <v>2.9044438153505325E-2</v>
       </c>
-      <c r="AW129" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX129" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA129">
-        <f t="shared" si="1"/>
-        <v>73.39807955180062</v>
-      </c>
     </row>
-    <row r="130" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
         <v>38961</v>
       </c>
@@ -20820,18 +19533,8 @@
       <c r="AV130" s="2">
         <v>5.1601152867078781E-2</v>
       </c>
-      <c r="AW130" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX130" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA130">
-        <f t="shared" si="1"/>
-        <v>76.512547442401811</v>
-      </c>
     </row>
-    <row r="131" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
         <v>38991</v>
       </c>
@@ -20976,18 +19679,8 @@
       <c r="AV131" s="2">
         <v>7.1439199149608612E-2</v>
       </c>
-      <c r="AW131" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX131" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA131">
-        <f t="shared" ref="BA131:BA194" si="2">(L131/AVERAGE(L131:L487))*100</f>
-        <v>168.88000118610054</v>
-      </c>
     </row>
-    <row r="132" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A132" s="1">
         <v>39022</v>
       </c>
@@ -21132,18 +19825,8 @@
       <c r="AV132" s="2">
         <v>4.5544255524873734E-2</v>
       </c>
-      <c r="AW132" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX132" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA132">
-        <f t="shared" si="2"/>
-        <v>66.748462608071392</v>
-      </c>
     </row>
-    <row r="133" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A133" s="1">
         <v>39052</v>
       </c>
@@ -21288,18 +19971,8 @@
       <c r="AV133" s="2">
         <v>4.551069438457489E-2</v>
       </c>
-      <c r="AW133" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX133" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA133">
-        <f t="shared" si="2"/>
-        <v>64.273277959162797</v>
-      </c>
     </row>
-    <row r="134" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A134" s="1">
         <v>39083</v>
       </c>
@@ -21444,18 +20117,8 @@
       <c r="AV134" s="2">
         <v>6.4854845404624939E-2</v>
       </c>
-      <c r="AW134" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX134" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA134">
-        <f t="shared" si="2"/>
-        <v>55.684379640485282</v>
-      </c>
     </row>
-    <row r="135" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A135" s="1">
         <v>39114</v>
       </c>
@@ -21600,18 +20263,8 @@
       <c r="AV135" s="2">
         <v>2.3102309554815292E-2</v>
       </c>
-      <c r="AW135" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX135" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA135">
-        <f t="shared" si="2"/>
-        <v>78.332634288557585</v>
-      </c>
     </row>
-    <row r="136" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A136" s="1">
         <v>39142</v>
       </c>
@@ -21756,18 +20409,8 @@
       <c r="AV136" s="2">
         <v>8.9631639420986176E-2</v>
       </c>
-      <c r="AW136" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX136" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA136">
-        <f t="shared" si="2"/>
-        <v>63.629737616620844</v>
-      </c>
     </row>
-    <row r="137" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A137" s="1">
         <v>39173</v>
       </c>
@@ -21912,18 +20555,8 @@
       <c r="AV137" s="2">
         <v>4.1663996875286102E-2</v>
       </c>
-      <c r="AW137" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX137" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA137">
-        <f t="shared" si="2"/>
-        <v>51.571781110156799</v>
-      </c>
     </row>
-    <row r="138" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
         <v>39203</v>
       </c>
@@ -22068,18 +20701,8 @@
       <c r="AV138" s="2">
         <v>5.5158987641334534E-2</v>
       </c>
-      <c r="AW138" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX138" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA138">
-        <f t="shared" si="2"/>
-        <v>50.093101578907529</v>
-      </c>
     </row>
-    <row r="139" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A139" s="1">
         <v>39234</v>
       </c>
@@ -22224,18 +20847,8 @@
       <c r="AV139" s="2">
         <v>6.9739431142807007E-2</v>
       </c>
-      <c r="AW139" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX139" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA139">
-        <f t="shared" si="2"/>
-        <v>59.083684409893102</v>
-      </c>
     </row>
-    <row r="140" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A140" s="1">
         <v>39264</v>
       </c>
@@ -22380,18 +20993,8 @@
       <c r="AV140" s="2">
         <v>3.2369792461395264E-2</v>
       </c>
-      <c r="AW140" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX140" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA140">
-        <f t="shared" si="2"/>
-        <v>57.73162135548332</v>
-      </c>
     </row>
-    <row r="141" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A141" s="1">
         <v>39295</v>
       </c>
@@ -22536,18 +21139,8 @@
       <c r="AV141" s="2">
         <v>2.2217284888029099E-2</v>
       </c>
-      <c r="AW141" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX141" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA141">
-        <f t="shared" si="2"/>
-        <v>43.833896652998881</v>
-      </c>
     </row>
-    <row r="142" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A142" s="1">
         <v>39326</v>
       </c>
@@ -22692,18 +21285,8 @@
       <c r="AV142" s="2">
         <v>4.3793793767690659E-2</v>
       </c>
-      <c r="AW142" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX142" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA142">
-        <f t="shared" si="2"/>
-        <v>87.138059756526957</v>
-      </c>
     </row>
-    <row r="143" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A143" s="1">
         <v>39356</v>
       </c>
@@ -22848,18 +21431,8 @@
       <c r="AV143" s="2">
         <v>7.723332941532135E-2</v>
       </c>
-      <c r="AW143" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX143" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA143">
-        <f t="shared" si="2"/>
-        <v>86.63624794954174</v>
-      </c>
     </row>
-    <row r="144" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A144" s="1">
         <v>39387</v>
       </c>
@@ -23004,18 +21577,8 @@
       <c r="AV144" s="2">
         <v>2.6963060721755028E-2</v>
       </c>
-      <c r="AW144" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX144" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA144">
-        <f t="shared" si="2"/>
-        <v>69.613563158188583</v>
-      </c>
     </row>
-    <row r="145" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A145" s="1">
         <v>39417</v>
       </c>
@@ -23160,18 +21723,8 @@
       <c r="AV145" s="2">
         <v>2.9164912179112434E-2</v>
       </c>
-      <c r="AW145" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX145" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA145">
-        <f t="shared" si="2"/>
-        <v>75.191560231749236</v>
-      </c>
     </row>
-    <row r="146" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A146" s="1">
         <v>39448</v>
       </c>
@@ -23316,18 +21869,8 @@
       <c r="AV146" s="2">
         <v>4.0482047945261002E-2</v>
       </c>
-      <c r="AW146" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX146" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA146">
-        <f t="shared" si="2"/>
-        <v>53.653665822042875</v>
-      </c>
     </row>
-    <row r="147" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A147" s="1">
         <v>39479</v>
       </c>
@@ -23472,18 +22015,8 @@
       <c r="AV147" s="2">
         <v>7.9463459551334381E-2</v>
       </c>
-      <c r="AW147" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX147" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA147">
-        <f t="shared" si="2"/>
-        <v>43.523460325066829</v>
-      </c>
     </row>
-    <row r="148" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A148" s="1">
         <v>39508</v>
       </c>
@@ -23628,18 +22161,8 @@
       <c r="AV148" s="2">
         <v>4.9544807523488998E-2</v>
       </c>
-      <c r="AW148" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX148" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA148">
-        <f t="shared" si="2"/>
-        <v>52.154726907350025</v>
-      </c>
     </row>
-    <row r="149" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A149" s="1">
         <v>39539</v>
       </c>
@@ -23784,18 +22307,8 @@
       <c r="AV149" s="2">
         <v>0.11084368079900742</v>
       </c>
-      <c r="AW149" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX149" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA149">
-        <f t="shared" si="2"/>
-        <v>44.589237275295332</v>
-      </c>
     </row>
-    <row r="150" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A150" s="1">
         <v>39569</v>
       </c>
@@ -23940,18 +22453,8 @@
       <c r="AV150" s="2">
         <v>5.8006409555673599E-2</v>
       </c>
-      <c r="AW150" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX150" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA150">
-        <f t="shared" si="2"/>
-        <v>59.926654943179756</v>
-      </c>
     </row>
-    <row r="151" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A151" s="1">
         <v>39600</v>
       </c>
@@ -24096,18 +22599,8 @@
       <c r="AV151" s="2">
         <v>0.10438413172960281</v>
       </c>
-      <c r="AW151" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX151" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA151">
-        <f t="shared" si="2"/>
-        <v>56.041240222132593</v>
-      </c>
     </row>
-    <row r="152" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A152" s="1">
         <v>39630</v>
       </c>
@@ -24252,18 +22745,8 @@
       <c r="AV152" s="2">
         <v>0.14531522989273071</v>
       </c>
-      <c r="AW152" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX152" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA152">
-        <f t="shared" si="2"/>
-        <v>68.041853321620565</v>
-      </c>
     </row>
-    <row r="153" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A153" s="1">
         <v>39661</v>
       </c>
@@ -24408,18 +22891,8 @@
       <c r="AV153" s="2">
         <v>4.6714939177036285E-2</v>
       </c>
-      <c r="AW153" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX153" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA153">
-        <f t="shared" si="2"/>
-        <v>56.113795240337772</v>
-      </c>
     </row>
-    <row r="154" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A154" s="1">
         <v>39692</v>
       </c>
@@ -24564,18 +23037,8 @@
       <c r="AV154" s="2">
         <v>6.5091453492641449E-2</v>
       </c>
-      <c r="AW154" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX154" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA154">
-        <f t="shared" si="2"/>
-        <v>57.540166682037523</v>
-      </c>
     </row>
-    <row r="155" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A155" s="1">
         <v>39722</v>
       </c>
@@ -24720,18 +23183,8 @@
       <c r="AV155" s="2">
         <v>4.0612310171127319E-2</v>
       </c>
-      <c r="AW155" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX155" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA155">
-        <f t="shared" si="2"/>
-        <v>52.314789148189369</v>
-      </c>
     </row>
-    <row r="156" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A156" s="1">
         <v>39753</v>
       </c>
@@ -24876,18 +23329,8 @@
       <c r="AV156" s="2">
         <v>4.3924853205680847E-2</v>
       </c>
-      <c r="AW156" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX156" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA156">
-        <f t="shared" si="2"/>
-        <v>44.85699280874055</v>
-      </c>
     </row>
-    <row r="157" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A157" s="1">
         <v>39783</v>
       </c>
@@ -25032,18 +23475,8 @@
       <c r="AV157" s="2">
         <v>2.9829598963260651E-2</v>
       </c>
-      <c r="AW157" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX157" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA157">
-        <f t="shared" si="2"/>
-        <v>43.265454522941852</v>
-      </c>
     </row>
-    <row r="158" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A158" s="1">
         <v>39814</v>
       </c>
@@ -25188,18 +23621,8 @@
       <c r="AV158" s="2">
         <v>2.4188810959458351E-2</v>
       </c>
-      <c r="AW158" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX158" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA158">
-        <f t="shared" si="2"/>
-        <v>36.907454694520922</v>
-      </c>
     </row>
-    <row r="159" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A159" s="1">
         <v>39845</v>
       </c>
@@ -25344,18 +23767,8 @@
       <c r="AV159" s="2">
         <v>1.8802646547555923E-2</v>
       </c>
-      <c r="AW159" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX159" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA159">
-        <f t="shared" si="2"/>
-        <v>46.155592129550605</v>
-      </c>
     </row>
-    <row r="160" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A160" s="1">
         <v>39873</v>
       </c>
@@ -25500,18 +23913,8 @@
       <c r="AV160" s="2">
         <v>4.5104432851076126E-2</v>
       </c>
-      <c r="AW160" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX160" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA160">
-        <f t="shared" si="2"/>
-        <v>36.329377882982108</v>
-      </c>
     </row>
-    <row r="161" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A161" s="1">
         <v>39904</v>
       </c>
@@ -25656,18 +24059,8 @@
       <c r="AV161" s="2">
         <v>3.6148063838481903E-2</v>
       </c>
-      <c r="AW161" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX161" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA161">
-        <f t="shared" si="2"/>
-        <v>86.085385272482213</v>
-      </c>
     </row>
-    <row r="162" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A162" s="1">
         <v>39934</v>
       </c>
@@ -25812,18 +24205,8 @@
       <c r="AV162" s="2">
         <v>3.2364785671234131E-2</v>
       </c>
-      <c r="AW162" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX162" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA162">
-        <f t="shared" si="2"/>
-        <v>58.109306770742073</v>
-      </c>
     </row>
-    <row r="163" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A163" s="1">
         <v>39965</v>
       </c>
@@ -25968,18 +24351,8 @@
       <c r="AV163" s="2">
         <v>2.6320736855268478E-2</v>
       </c>
-      <c r="AW163" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX163" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA163">
-        <f t="shared" si="2"/>
-        <v>60.078908139991995</v>
-      </c>
     </row>
-    <row r="164" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A164" s="1">
         <v>39995</v>
       </c>
@@ -26124,18 +24497,8 @@
       <c r="AV164" s="2">
         <v>3.4387893974781036E-2</v>
       </c>
-      <c r="AW164" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX164" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA164">
-        <f t="shared" si="2"/>
-        <v>57.012567016507788</v>
-      </c>
     </row>
-    <row r="165" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A165" s="1">
         <v>40026</v>
       </c>
@@ -26280,18 +24643,8 @@
       <c r="AV165" s="2">
         <v>8.0025605857372284E-3</v>
       </c>
-      <c r="AW165" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX165" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA165">
-        <f t="shared" si="2"/>
-        <v>55.48411805588259</v>
-      </c>
     </row>
-    <row r="166" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A166" s="1">
         <v>40057</v>
       </c>
@@ -26436,18 +24789,8 @@
       <c r="AV166" s="2">
         <v>9.8638035356998444E-2</v>
       </c>
-      <c r="AW166" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX166" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA166">
-        <f t="shared" si="2"/>
-        <v>89.501764713702059</v>
-      </c>
     </row>
-    <row r="167" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A167" s="1">
         <v>40087</v>
       </c>
@@ -26592,18 +24935,8 @@
       <c r="AV167" s="2">
         <v>5.3339023143053055E-2</v>
       </c>
-      <c r="AW167" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX167" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA167">
-        <f t="shared" si="2"/>
-        <v>62.107374655697775</v>
-      </c>
     </row>
-    <row r="168" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A168" s="1">
         <v>40118</v>
       </c>
@@ -26748,18 +25081,8 @@
       <c r="AV168" s="2">
         <v>5.3367894142866135E-2</v>
       </c>
-      <c r="AW168" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX168" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA168">
-        <f t="shared" si="2"/>
-        <v>54.265711262882085</v>
-      </c>
     </row>
-    <row r="169" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A169" s="1">
         <v>40148</v>
       </c>
@@ -26904,18 +25227,8 @@
       <c r="AV169" s="2">
         <v>2.4137098342180252E-2</v>
       </c>
-      <c r="AW169" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX169" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA169">
-        <f t="shared" si="2"/>
-        <v>53.049154782377371</v>
-      </c>
     </row>
-    <row r="170" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A170" s="1">
         <v>40179</v>
       </c>
@@ -27060,18 +25373,8 @@
       <c r="AV170" s="2">
         <v>2.2181965410709381E-2</v>
       </c>
-      <c r="AW170" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX170" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA170">
-        <f t="shared" si="2"/>
-        <v>52.906583490162731</v>
-      </c>
     </row>
-    <row r="171" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A171" s="1">
         <v>40210</v>
       </c>
@@ -27216,18 +25519,8 @@
       <c r="AV171" s="2">
         <v>5.0973966717720032E-2</v>
       </c>
-      <c r="AW171" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX171" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA171">
-        <f t="shared" si="2"/>
-        <v>73.500054082271049</v>
-      </c>
     </row>
-    <row r="172" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A172" s="1">
         <v>40238</v>
       </c>
@@ -27372,18 +25665,8 @@
       <c r="AV172" s="2">
         <v>1.6969861462712288E-2</v>
       </c>
-      <c r="AW172" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX172" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA172">
-        <f t="shared" si="2"/>
-        <v>54.244468714052488</v>
-      </c>
     </row>
-    <row r="173" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A173" s="1">
         <v>40269</v>
       </c>
@@ -27528,18 +25811,8 @@
       <c r="AV173" s="2">
         <v>0.11389521509408951</v>
       </c>
-      <c r="AW173" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX173" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA173">
-        <f t="shared" si="2"/>
-        <v>80.773653265084988</v>
-      </c>
     </row>
-    <row r="174" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A174" s="1">
         <v>40299</v>
       </c>
@@ -27684,18 +25957,8 @@
       <c r="AV174" s="2">
         <v>3.4120377153158188E-2</v>
       </c>
-      <c r="AW174" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX174" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA174">
-        <f t="shared" si="2"/>
-        <v>93.019387092433874</v>
-      </c>
     </row>
-    <row r="175" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A175" s="1">
         <v>40330</v>
       </c>
@@ -27840,18 +26103,8 @@
       <c r="AV175" s="2">
         <v>4.1279669851064682E-2</v>
       </c>
-      <c r="AW175" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX175" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA175">
-        <f t="shared" si="2"/>
-        <v>53.286848911864482</v>
-      </c>
     </row>
-    <row r="176" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A176" s="1">
         <v>40360</v>
       </c>
@@ -27996,18 +26249,8 @@
       <c r="AV176" s="2">
         <v>3.5169161856174469E-2</v>
       </c>
-      <c r="AW176" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX176" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA176">
-        <f t="shared" si="2"/>
-        <v>31.19520556855991</v>
-      </c>
     </row>
-    <row r="177" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A177" s="1">
         <v>40391</v>
       </c>
@@ -28152,18 +26395,8 @@
       <c r="AV177" s="2">
         <v>5.2566364407539368E-2</v>
       </c>
-      <c r="AW177" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX177" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA177">
-        <f t="shared" si="2"/>
-        <v>46.558026001477728</v>
-      </c>
     </row>
-    <row r="178" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A178" s="1">
         <v>40422</v>
       </c>
@@ -28308,18 +26541,8 @@
       <c r="AV178" s="2">
         <v>4.2200028896331787E-2</v>
       </c>
-      <c r="AW178" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX178" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA178">
-        <f t="shared" si="2"/>
-        <v>47.975301267489897</v>
-      </c>
     </row>
-    <row r="179" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A179" s="1">
         <v>40452</v>
       </c>
@@ -28464,18 +26687,8 @@
       <c r="AV179" s="2">
         <v>1.6439797356724739E-2</v>
       </c>
-      <c r="AW179" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX179" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA179">
-        <f t="shared" si="2"/>
-        <v>40.06696836075028</v>
-      </c>
     </row>
-    <row r="180" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A180" s="1">
         <v>40483</v>
       </c>
@@ -28620,18 +26833,8 @@
       <c r="AV180" s="2">
         <v>6.6384822130203247E-2</v>
       </c>
-      <c r="AW180" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX180" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA180">
-        <f t="shared" si="2"/>
-        <v>96.218746489440747</v>
-      </c>
     </row>
-    <row r="181" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A181" s="1">
         <v>40513</v>
       </c>
@@ -28776,18 +26979,8 @@
       <c r="AV181" s="2">
         <v>0.12840363383293152</v>
       </c>
-      <c r="AW181" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX181" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA181">
-        <f t="shared" si="2"/>
-        <v>74.652451454424451</v>
-      </c>
     </row>
-    <row r="182" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A182" s="1">
         <v>40544</v>
       </c>
@@ -28932,18 +27125,8 @@
       <c r="AV182" s="2">
         <v>3.258272260427475E-2</v>
       </c>
-      <c r="AW182" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX182" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA182">
-        <f t="shared" si="2"/>
-        <v>65.846202962827888</v>
-      </c>
     </row>
-    <row r="183" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A183" s="1">
         <v>40575</v>
       </c>
@@ -29088,18 +27271,8 @@
       <c r="AV183" s="2">
         <v>2.7076160535216331E-2</v>
       </c>
-      <c r="AW183" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX183" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA183">
-        <f t="shared" si="2"/>
-        <v>56.06353449104693</v>
-      </c>
     </row>
-    <row r="184" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A184" s="1">
         <v>40603</v>
       </c>
@@ -29244,18 +27417,8 @@
       <c r="AV184" s="2">
         <v>6.3217431306838989E-2</v>
       </c>
-      <c r="AW184" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX184" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA184">
-        <f t="shared" si="2"/>
-        <v>74.258394511417862</v>
-      </c>
     </row>
-    <row r="185" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A185" s="1">
         <v>40634</v>
       </c>
@@ -29400,18 +27563,8 @@
       <c r="AV185" s="2">
         <v>0.12880603969097137</v>
       </c>
-      <c r="AW185" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX185" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA185">
-        <f t="shared" si="2"/>
-        <v>37.611284353261311</v>
-      </c>
     </row>
-    <row r="186" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A186" s="1">
         <v>40664</v>
       </c>
@@ -29556,18 +27709,8 @@
       <c r="AV186" s="2">
         <v>6.7835338413715363E-2</v>
       </c>
-      <c r="AW186" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX186" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA186">
-        <f t="shared" si="2"/>
-        <v>28.919460070107249</v>
-      </c>
     </row>
-    <row r="187" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A187" s="1">
         <v>40695</v>
       </c>
@@ -29712,18 +27855,8 @@
       <c r="AV187" s="2">
         <v>8.2814246416091919E-2</v>
       </c>
-      <c r="AW187" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX187" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA187">
-        <f t="shared" si="2"/>
-        <v>50.57865754387911</v>
-      </c>
     </row>
-    <row r="188" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A188" s="1">
         <v>40725</v>
       </c>
@@ -29868,18 +28001,8 @@
       <c r="AV188" s="2">
         <v>2.9498524963855743E-2</v>
       </c>
-      <c r="AW188" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX188" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA188">
-        <f t="shared" si="2"/>
-        <v>37.329187812796093</v>
-      </c>
     </row>
-    <row r="189" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A189" s="1">
         <v>40756</v>
       </c>
@@ -30024,18 +28147,8 @@
       <c r="AV189" s="2">
         <v>8.99314284324646E-2</v>
       </c>
-      <c r="AW189" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX189" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA189">
-        <f t="shared" si="2"/>
-        <v>41.419754008548338</v>
-      </c>
     </row>
-    <row r="190" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A190" s="1">
         <v>40787</v>
       </c>
@@ -30180,18 +28293,8 @@
       <c r="AV190" s="2">
         <v>8.167613297700882E-2</v>
       </c>
-      <c r="AW190" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX190" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA190">
-        <f t="shared" si="2"/>
-        <v>38.628597968285625</v>
-      </c>
     </row>
-    <row r="191" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A191" s="1">
         <v>40817</v>
       </c>
@@ -30336,18 +28439,8 @@
       <c r="AV191" s="2">
         <v>9.8331868648529053E-2</v>
       </c>
-      <c r="AW191" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX191" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA191">
-        <f t="shared" si="2"/>
-        <v>51.070841702273597</v>
-      </c>
     </row>
-    <row r="192" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A192" s="1">
         <v>40848</v>
       </c>
@@ -30492,18 +28585,8 @@
       <c r="AV192" s="2">
         <v>2.8464686125516891E-2</v>
       </c>
-      <c r="AW192" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX192" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA192">
-        <f t="shared" si="2"/>
-        <v>80.795056324908217</v>
-      </c>
     </row>
-    <row r="193" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A193" s="1">
         <v>40878</v>
       </c>
@@ -30648,18 +28731,8 @@
       <c r="AV193" s="2">
         <v>2.662406861782074E-2</v>
       </c>
-      <c r="AW193" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX193" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA193">
-        <f t="shared" si="2"/>
-        <v>75.353340593079707</v>
-      </c>
     </row>
-    <row r="194" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A194" s="1">
         <v>40909</v>
       </c>
@@ -30804,18 +28877,8 @@
       <c r="AV194" s="2">
         <v>5.2005942910909653E-2</v>
       </c>
-      <c r="AW194" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX194" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA194">
-        <f t="shared" si="2"/>
-        <v>76.526492121450147</v>
-      </c>
     </row>
-    <row r="195" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A195" s="1">
         <v>40940</v>
       </c>
@@ -30960,18 +29023,8 @@
       <c r="AV195" s="2">
         <v>5.3323175758123398E-2</v>
       </c>
-      <c r="AW195" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX195" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA195">
-        <f t="shared" ref="BA195:BA258" si="3">(L195/AVERAGE(L195:L551))*100</f>
-        <v>111.56171587682036</v>
-      </c>
     </row>
-    <row r="196" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A196" s="1">
         <v>40969</v>
       </c>
@@ -31116,18 +29169,8 @@
       <c r="AV196" s="2">
         <v>6.2073245644569397E-2</v>
       </c>
-      <c r="AW196" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX196" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA196">
-        <f t="shared" si="3"/>
-        <v>85.09566348387942</v>
-      </c>
     </row>
-    <row r="197" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A197" s="1">
         <v>41000</v>
       </c>
@@ -31272,18 +29315,8 @@
       <c r="AV197" s="2">
         <v>6.8298235535621643E-2</v>
       </c>
-      <c r="AW197" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX197" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA197">
-        <f t="shared" si="3"/>
-        <v>109.04781202914128</v>
-      </c>
     </row>
-    <row r="198" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A198" s="1">
         <v>41030</v>
       </c>
@@ -31428,18 +29461,8 @@
       <c r="AV198" s="2">
         <v>2.5289017707109451E-2</v>
       </c>
-      <c r="AW198" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX198" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA198">
-        <f t="shared" si="3"/>
-        <v>65.482797310477537</v>
-      </c>
     </row>
-    <row r="199" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A199" s="1">
         <v>41061</v>
       </c>
@@ -31584,18 +29607,8 @@
       <c r="AV199" s="2">
         <v>2.992556057870388E-2</v>
       </c>
-      <c r="AW199" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX199" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA199">
-        <f t="shared" si="3"/>
-        <v>65.113048752125025</v>
-      </c>
     </row>
-    <row r="200" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A200" s="1">
         <v>41091</v>
       </c>
@@ -31740,18 +29753,8 @@
       <c r="AV200" s="2">
         <v>3.8507450371980667E-2</v>
       </c>
-      <c r="AW200" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX200" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA200">
-        <f t="shared" si="3"/>
-        <v>66.359390910283082</v>
-      </c>
     </row>
-    <row r="201" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A201" s="1">
         <v>41122</v>
       </c>
@@ -31896,18 +29899,8 @@
       <c r="AV201" s="2">
         <v>5.6053809821605682E-2</v>
       </c>
-      <c r="AW201" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX201" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA201">
-        <f t="shared" si="3"/>
-        <v>40.985394751299033</v>
-      </c>
     </row>
-    <row r="202" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A202" s="1">
         <v>41153</v>
       </c>
@@ -32052,18 +30045,8 @@
       <c r="AV202" s="2">
         <v>3.6648832261562347E-2</v>
       </c>
-      <c r="AW202" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX202" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA202">
-        <f t="shared" si="3"/>
-        <v>49.438002231470904</v>
-      </c>
     </row>
-    <row r="203" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A203" s="1">
         <v>41183</v>
       </c>
@@ -32208,18 +30191,8 @@
       <c r="AV203" s="2">
         <v>2.7913467958569527E-2</v>
       </c>
-      <c r="AW203" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX203" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA203">
-        <f t="shared" si="3"/>
-        <v>45.977498558973977</v>
-      </c>
     </row>
-    <row r="204" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A204" s="1">
         <v>41214</v>
       </c>
@@ -32364,18 +30337,8 @@
       <c r="AV204" s="2">
         <v>4.6127099543809891E-2</v>
       </c>
-      <c r="AW204" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX204" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA204">
-        <f t="shared" si="3"/>
-        <v>40.887978517306756</v>
-      </c>
     </row>
-    <row r="205" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A205" s="1">
         <v>41244</v>
       </c>
@@ -32520,18 +30483,8 @@
       <c r="AV205" s="2">
         <v>4.6598322689533234E-2</v>
       </c>
-      <c r="AW205" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX205" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA205">
-        <f t="shared" si="3"/>
-        <v>40.948380738046829</v>
-      </c>
     </row>
-    <row r="206" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A206" s="1">
         <v>41275</v>
       </c>
@@ -32676,18 +30629,8 @@
       <c r="AV206" s="2">
         <v>7.3391802608966827E-2</v>
       </c>
-      <c r="AW206" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX206" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA206">
-        <f t="shared" si="3"/>
-        <v>45.378290848372991</v>
-      </c>
     </row>
-    <row r="207" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A207" s="1">
         <v>41306</v>
       </c>
@@ -32832,18 +30775,8 @@
       <c r="AV207" s="2">
         <v>3.5523977130651474E-2</v>
       </c>
-      <c r="AW207" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX207" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA207">
-        <f t="shared" si="3"/>
-        <v>61.709336370685918</v>
-      </c>
     </row>
-    <row r="208" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A208" s="1">
         <v>41334</v>
       </c>
@@ -32988,18 +30921,8 @@
       <c r="AV208" s="2">
         <v>4.9641869962215424E-2</v>
       </c>
-      <c r="AW208" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX208" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA208">
-        <f t="shared" si="3"/>
-        <v>54.358561085988654</v>
-      </c>
     </row>
-    <row r="209" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A209" s="1">
         <v>41365</v>
       </c>
@@ -33144,18 +31067,8 @@
       <c r="AV209" s="2">
         <v>4.4923629611730576E-2</v>
       </c>
-      <c r="AW209" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX209" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA209">
-        <f t="shared" si="3"/>
-        <v>85.331647418411279</v>
-      </c>
     </row>
-    <row r="210" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A210" s="1">
         <v>41395</v>
       </c>
@@ -33300,18 +31213,8 @@
       <c r="AV210" s="2">
         <v>1.4431055635213852E-2</v>
       </c>
-      <c r="AW210" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX210" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA210">
-        <f t="shared" si="3"/>
-        <v>36.090660059998882</v>
-      </c>
     </row>
-    <row r="211" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A211" s="1">
         <v>41426</v>
       </c>
@@ -33456,18 +31359,8 @@
       <c r="AV211" s="2">
         <v>3.4247878938913345E-2</v>
       </c>
-      <c r="AW211" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX211" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA211">
-        <f t="shared" si="3"/>
-        <v>54.361251422002788</v>
-      </c>
     </row>
-    <row r="212" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A212" s="1">
         <v>41456</v>
       </c>
@@ -33612,18 +31505,8 @@
       <c r="AV212" s="2">
         <v>6.2833800911903381E-2</v>
       </c>
-      <c r="AW212" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX212" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA212">
-        <f t="shared" si="3"/>
-        <v>34.890550501849638</v>
-      </c>
     </row>
-    <row r="213" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A213" s="1">
         <v>41487</v>
       </c>
@@ -33768,18 +31651,8 @@
       <c r="AV213" s="2">
         <v>3.4436579793691635E-2</v>
       </c>
-      <c r="AW213" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX213" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA213">
-        <f t="shared" si="3"/>
-        <v>35.336937587394111</v>
-      </c>
     </row>
-    <row r="214" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A214" s="1">
         <v>41518</v>
       </c>
@@ -33924,18 +31797,8 @@
       <c r="AV214" s="2">
         <v>5.7723388075828552E-2</v>
       </c>
-      <c r="AW214" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX214" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA214">
-        <f t="shared" si="3"/>
-        <v>47.840139908753024</v>
-      </c>
     </row>
-    <row r="215" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A215" s="1">
         <v>41548</v>
       </c>
@@ -34080,18 +31943,8 @@
       <c r="AV215" s="2">
         <v>7.5952112674713135E-2</v>
       </c>
-      <c r="AW215" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX215" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA215">
-        <f t="shared" si="3"/>
-        <v>43.867086261098741</v>
-      </c>
     </row>
-    <row r="216" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A216" s="1">
         <v>41579</v>
       </c>
@@ -34236,18 +32089,8 @@
       <c r="AV216" s="2">
         <v>3.408445417881012E-2</v>
       </c>
-      <c r="AW216" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX216" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA216">
-        <f t="shared" si="3"/>
-        <v>64.250525494716982</v>
-      </c>
     </row>
-    <row r="217" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A217" s="1">
         <v>41609</v>
       </c>
@@ -34392,18 +32235,8 @@
       <c r="AV217" s="2">
         <v>8.7427146732807159E-2</v>
       </c>
-      <c r="AW217" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX217" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA217">
-        <f t="shared" si="3"/>
-        <v>45.901024630078048</v>
-      </c>
     </row>
-    <row r="218" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A218" s="1">
         <v>41640</v>
       </c>
@@ -34548,18 +32381,8 @@
       <c r="AV218" s="2">
         <v>4.7132756561040878E-2</v>
       </c>
-      <c r="AW218" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX218" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA218">
-        <f t="shared" si="3"/>
-        <v>35.113446948257568</v>
-      </c>
     </row>
-    <row r="219" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A219" s="1">
         <v>41671</v>
       </c>
@@ -34704,18 +32527,8 @@
       <c r="AV219" s="2">
         <v>2.9033595696091652E-2</v>
       </c>
-      <c r="AW219" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX219" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA219">
-        <f t="shared" si="3"/>
-        <v>37.435767240940734</v>
-      </c>
     </row>
-    <row r="220" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A220" s="1">
         <v>41699</v>
       </c>
@@ -34860,18 +32673,8 @@
       <c r="AV220" s="2">
         <v>5.5813953280448914E-2</v>
       </c>
-      <c r="AW220" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX220" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA220">
-        <f t="shared" si="3"/>
-        <v>76.756362809834684</v>
-      </c>
     </row>
-    <row r="221" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A221" s="1">
         <v>41730</v>
       </c>
@@ -35016,18 +32819,8 @@
       <c r="AV221" s="2">
         <v>3.5493157804012299E-2</v>
       </c>
-      <c r="AW221" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX221" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA221">
-        <f t="shared" si="3"/>
-        <v>53.810899003931056</v>
-      </c>
     </row>
-    <row r="222" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A222" s="1">
         <v>41760</v>
       </c>
@@ -35172,18 +32965,8 @@
       <c r="AV222" s="2">
         <v>4.5155219733715057E-2</v>
       </c>
-      <c r="AW222" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX222" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA222">
-        <f t="shared" si="3"/>
-        <v>57.331685411396002</v>
-      </c>
     </row>
-    <row r="223" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A223" s="1">
         <v>41791</v>
       </c>
@@ -35328,18 +33111,8 @@
       <c r="AV223" s="2">
         <v>3.9657361805438995E-2</v>
       </c>
-      <c r="AW223" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX223" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA223">
-        <f t="shared" si="3"/>
-        <v>27.876229150511222</v>
-      </c>
     </row>
-    <row r="224" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A224" s="1">
         <v>41821</v>
       </c>
@@ -35484,18 +33257,8 @@
       <c r="AV224" s="2">
         <v>5.0992392003536224E-2</v>
       </c>
-      <c r="AW224" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX224" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA224">
-        <f t="shared" si="3"/>
-        <v>71.013053858153995</v>
-      </c>
     </row>
-    <row r="225" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A225" s="1">
         <v>41852</v>
       </c>
@@ -35640,18 +33403,8 @@
       <c r="AV225" s="2">
         <v>4.1380450129508972E-2</v>
       </c>
-      <c r="AW225" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX225" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA225">
-        <f t="shared" si="3"/>
-        <v>49.492134272072676</v>
-      </c>
     </row>
-    <row r="226" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A226" s="1">
         <v>41883</v>
       </c>
@@ -35796,18 +33549,8 @@
       <c r="AV226" s="2">
         <v>4.8169557005167007E-2</v>
       </c>
-      <c r="AW226" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX226" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA226">
-        <f t="shared" si="3"/>
-        <v>55.3016329490667</v>
-      </c>
     </row>
-    <row r="227" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A227" s="1">
         <v>41913</v>
       </c>
@@ -35952,18 +33695,8 @@
       <c r="AV227" s="2">
         <v>4.1821915656328201E-2</v>
       </c>
-      <c r="AW227" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX227" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA227">
-        <f t="shared" si="3"/>
-        <v>29.158041300087952</v>
-      </c>
     </row>
-    <row r="228" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A228" s="1">
         <v>41944</v>
       </c>
@@ -36108,18 +33841,8 @@
       <c r="AV228" s="2">
         <v>2.8165614232420921E-2</v>
       </c>
-      <c r="AW228" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX228" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA228">
-        <f t="shared" si="3"/>
-        <v>46.038089173688931</v>
-      </c>
     </row>
-    <row r="229" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A229" s="1">
         <v>41974</v>
       </c>
@@ -36264,18 +33987,8 @@
       <c r="AV229" s="2">
         <v>5.660787969827652E-2</v>
       </c>
-      <c r="AW229" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX229" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA229">
-        <f t="shared" si="3"/>
-        <v>30.943947471065353</v>
-      </c>
     </row>
-    <row r="230" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A230" s="1">
         <v>42005</v>
       </c>
@@ -36420,18 +34133,8 @@
       <c r="AV230" s="2">
         <v>5.4445702582597733E-2</v>
       </c>
-      <c r="AW230" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX230" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA230">
-        <f t="shared" si="3"/>
-        <v>35.218013121923981</v>
-      </c>
     </row>
-    <row r="231" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A231" s="1">
         <v>42036</v>
       </c>
@@ -36576,18 +34279,8 @@
       <c r="AV231" s="2">
         <v>5.0173327326774597E-2</v>
       </c>
-      <c r="AW231" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX231" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA231">
-        <f t="shared" si="3"/>
-        <v>39.26825686788932</v>
-      </c>
     </row>
-    <row r="232" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A232" s="1">
         <v>42064</v>
       </c>
@@ -36732,18 +34425,8 @@
       <c r="AV232" s="2">
         <v>5.3548626601696014E-2</v>
       </c>
-      <c r="AW232" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX232" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA232">
-        <f t="shared" si="3"/>
-        <v>48.217860992525054</v>
-      </c>
     </row>
-    <row r="233" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A233" s="1">
         <v>42095</v>
       </c>
@@ -36888,18 +34571,8 @@
       <c r="AV233" s="2">
         <v>2.9758108779788017E-2</v>
       </c>
-      <c r="AW233" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX233" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA233">
-        <f t="shared" si="3"/>
-        <v>60.289174853318464</v>
-      </c>
     </row>
-    <row r="234" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A234" s="1">
         <v>42125</v>
       </c>
@@ -37044,18 +34717,8 @@
       <c r="AV234" s="2">
         <v>5.1306169480085373E-2</v>
       </c>
-      <c r="AW234" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX234" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA234">
-        <f t="shared" si="3"/>
-        <v>35.343534893623804</v>
-      </c>
     </row>
-    <row r="235" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A235" s="1">
         <v>42156</v>
       </c>
@@ -37200,18 +34863,8 @@
       <c r="AV235" s="2">
         <v>6.9288067519664764E-2</v>
       </c>
-      <c r="AW235" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX235" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA235">
-        <f t="shared" si="3"/>
-        <v>38.193028498093724</v>
-      </c>
     </row>
-    <row r="236" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A236" s="1">
         <v>42186</v>
       </c>
@@ -37356,18 +35009,8 @@
       <c r="AV236" s="2">
         <v>5.6279491633176804E-2</v>
       </c>
-      <c r="AW236" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX236" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA236">
-        <f t="shared" si="3"/>
-        <v>86.2488227708306</v>
-      </c>
     </row>
-    <row r="237" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A237" s="1">
         <v>42217</v>
       </c>
@@ -37512,18 +35155,8 @@
       <c r="AV237" s="2">
         <v>3.2984636723995209E-2</v>
       </c>
-      <c r="AW237" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX237" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA237">
-        <f t="shared" si="3"/>
-        <v>52.467378883348147</v>
-      </c>
     </row>
-    <row r="238" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A238" s="1">
         <v>42248</v>
       </c>
@@ -37668,18 +35301,8 @@
       <c r="AV238" s="2">
         <v>5.6551244109869003E-2</v>
       </c>
-      <c r="AW238" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX238" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA238">
-        <f t="shared" si="3"/>
-        <v>49.273699355452777</v>
-      </c>
     </row>
-    <row r="239" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A239" s="1">
         <v>42278</v>
       </c>
@@ -37824,18 +35447,8 @@
       <c r="AV239" s="2">
         <v>2.4329913780093193E-2</v>
       </c>
-      <c r="AW239" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX239" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA239">
-        <f t="shared" si="3"/>
-        <v>32.397490343067076</v>
-      </c>
     </row>
-    <row r="240" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A240" s="1">
         <v>42309</v>
       </c>
@@ -37980,18 +35593,8 @@
       <c r="AV240" s="2">
         <v>5.4794520139694214E-2</v>
       </c>
-      <c r="AW240" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX240" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA240">
-        <f t="shared" si="3"/>
-        <v>57.08113905169273</v>
-      </c>
     </row>
-    <row r="241" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A241" s="1">
         <v>42339</v>
       </c>
@@ -38136,18 +35739,8 @@
       <c r="AV241" s="2">
         <v>6.3938617706298828E-2</v>
       </c>
-      <c r="AW241" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX241" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA241">
-        <f t="shared" si="3"/>
-        <v>54.39008282662401</v>
-      </c>
     </row>
-    <row r="242" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A242" s="1">
         <v>42370</v>
       </c>
@@ -38292,18 +35885,8 @@
       <c r="AV242" s="2">
         <v>6.9521687924861908E-2</v>
       </c>
-      <c r="AW242" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX242" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA242">
-        <f t="shared" si="3"/>
-        <v>80.613321327928205</v>
-      </c>
     </row>
-    <row r="243" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A243" s="1">
         <v>42401</v>
       </c>
@@ -38448,18 +36031,8 @@
       <c r="AV243" s="2">
         <v>3.9142772555351257E-2</v>
       </c>
-      <c r="AW243" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX243" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA243">
-        <f t="shared" si="3"/>
-        <v>57.77275097902497</v>
-      </c>
     </row>
-    <row r="244" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A244" s="1">
         <v>42430</v>
       </c>
@@ -38604,18 +36177,8 @@
       <c r="AV244" s="2">
         <v>4.5267302542924881E-2</v>
       </c>
-      <c r="AW244" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX244" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA244">
-        <f t="shared" si="3"/>
-        <v>58.99735607180866</v>
-      </c>
     </row>
-    <row r="245" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A245" s="1">
         <v>42461</v>
       </c>
@@ -38760,18 +36323,8 @@
       <c r="AV245" s="2">
         <v>1.3942464254796505E-2</v>
       </c>
-      <c r="AW245" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX245" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA245">
-        <f t="shared" si="3"/>
-        <v>41.660372440913889</v>
-      </c>
     </row>
-    <row r="246" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A246" s="1">
         <v>42491</v>
       </c>
@@ -38916,18 +36469,8 @@
       <c r="AV246" s="2">
         <v>2.276141569018364E-2</v>
       </c>
-      <c r="AW246" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX246" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA246">
-        <f t="shared" si="3"/>
-        <v>51.006928744344982</v>
-      </c>
     </row>
-    <row r="247" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A247" s="1">
         <v>42522</v>
       </c>
@@ -39072,18 +36615,8 @@
       <c r="AV247" s="2">
         <v>2.8319252654910088E-2</v>
       </c>
-      <c r="AW247" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX247" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA247">
-        <f t="shared" si="3"/>
-        <v>34.386559959479577</v>
-      </c>
     </row>
-    <row r="248" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A248" s="1">
         <v>42552</v>
       </c>
@@ -39228,18 +36761,8 @@
       <c r="AV248" s="2">
         <v>2.94652059674263E-2</v>
       </c>
-      <c r="AW248" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX248" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA248">
-        <f t="shared" si="3"/>
-        <v>42.792492621171888</v>
-      </c>
     </row>
-    <row r="249" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A249" s="1">
         <v>42583</v>
       </c>
@@ -39384,18 +36907,8 @@
       <c r="AV249" s="2">
         <v>3.6179449409246445E-2</v>
       </c>
-      <c r="AW249" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX249" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA249">
-        <f t="shared" si="3"/>
-        <v>32.585004828323591</v>
-      </c>
     </row>
-    <row r="250" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A250" s="1">
         <v>42614</v>
       </c>
@@ -39540,18 +37053,8 @@
       <c r="AV250" s="2">
         <v>3.0248034745454788E-2</v>
       </c>
-      <c r="AW250" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX250" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA250">
-        <f t="shared" si="3"/>
-        <v>65.432263028539964</v>
-      </c>
     </row>
-    <row r="251" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A251" s="1">
         <v>42644</v>
       </c>
@@ -39696,18 +37199,8 @@
       <c r="AV251" s="2">
         <v>2.9449298977851868E-2</v>
       </c>
-      <c r="AW251" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX251" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA251">
-        <f t="shared" si="3"/>
-        <v>29.560902078196843</v>
-      </c>
     </row>
-    <row r="252" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A252" s="1">
         <v>42675</v>
       </c>
@@ -39852,18 +37345,8 @@
       <c r="AV252" s="2">
         <v>3.076765313744545E-2</v>
       </c>
-      <c r="AW252" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX252" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA252">
-        <f t="shared" si="3"/>
-        <v>52.841685529957161</v>
-      </c>
     </row>
-    <row r="253" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A253" s="1">
         <v>42705</v>
       </c>
@@ -40008,18 +37491,8 @@
       <c r="AV253" s="2">
         <v>3.2204389572143555E-2</v>
       </c>
-      <c r="AW253" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX253" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA253">
-        <f t="shared" si="3"/>
-        <v>64.537639638754058</v>
-      </c>
     </row>
-    <row r="254" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A254" s="1">
         <v>42736</v>
       </c>
@@ -40164,18 +37637,8 @@
       <c r="AV254" s="2">
         <v>5.0648298114538193E-2</v>
       </c>
-      <c r="AW254" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX254" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA254">
-        <f t="shared" si="3"/>
-        <v>70.717519217322263</v>
-      </c>
     </row>
-    <row r="255" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A255" s="1">
         <v>42767</v>
       </c>
@@ -40320,18 +37783,8 @@
       <c r="AV255" s="2">
         <v>3.8550499826669693E-2</v>
       </c>
-      <c r="AW255" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX255" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA255">
-        <f t="shared" si="3"/>
-        <v>79.093472779628527</v>
-      </c>
     </row>
-    <row r="256" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A256" s="1">
         <v>42795</v>
       </c>
@@ -40476,18 +37929,8 @@
       <c r="AV256" s="2">
         <v>5.2874445915222168E-2</v>
       </c>
-      <c r="AW256" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX256" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA256">
-        <f t="shared" si="3"/>
-        <v>68.893967149992704</v>
-      </c>
     </row>
-    <row r="257" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A257" s="1">
         <v>42826</v>
       </c>
@@ -40632,18 +38075,8 @@
       <c r="AV257" s="2">
         <v>4.2030051350593567E-2</v>
       </c>
-      <c r="AW257" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX257" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA257">
-        <f t="shared" si="3"/>
-        <v>117.47842634327002</v>
-      </c>
     </row>
-    <row r="258" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A258" s="1">
         <v>42856</v>
       </c>
@@ -40788,18 +38221,8 @@
       <c r="AV258" s="2">
         <v>1.0154346004128456E-2</v>
       </c>
-      <c r="AW258" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX258" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA258">
-        <f t="shared" si="3"/>
-        <v>75.447947694619771</v>
-      </c>
     </row>
-    <row r="259" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A259" s="1">
         <v>42887</v>
       </c>
@@ -40944,18 +38367,8 @@
       <c r="AV259" s="2">
         <v>3.6119710654020309E-2</v>
       </c>
-      <c r="AW259" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX259" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA259">
-        <f t="shared" ref="BA259:BA322" si="4">(L259/AVERAGE(L259:L615))*100</f>
-        <v>59.055058180792408</v>
-      </c>
     </row>
-    <row r="260" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A260" s="1">
         <v>42917</v>
       </c>
@@ -41100,18 +38513,8 @@
       <c r="AV260" s="2">
         <v>4.2388595640659332E-2</v>
       </c>
-      <c r="AW260" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX260" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA260">
-        <f t="shared" si="4"/>
-        <v>98.352244275994281</v>
-      </c>
     </row>
-    <row r="261" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A261" s="1">
         <v>42948</v>
       </c>
@@ -41256,18 +38659,8 @@
       <c r="AV261" s="2">
         <v>3.7385173141956329E-2</v>
       </c>
-      <c r="AW261" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX261" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA261">
-        <f t="shared" si="4"/>
-        <v>136.21511434065755</v>
-      </c>
     </row>
-    <row r="262" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A262" s="1">
         <v>42979</v>
       </c>
@@ -41412,18 +38805,8 @@
       <c r="AV262" s="2">
         <v>8.9878663420677185E-2</v>
       </c>
-      <c r="AW262" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX262" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA262">
-        <f t="shared" si="4"/>
-        <v>132.72553227557046</v>
-      </c>
     </row>
-    <row r="263" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A263" s="1">
         <v>43009</v>
       </c>
@@ -41568,18 +38951,8 @@
       <c r="AV263" s="2">
         <v>3.6523010581731796E-2</v>
       </c>
-      <c r="AW263" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX263" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA263">
-        <f t="shared" si="4"/>
-        <v>66.095803153773019</v>
-      </c>
     </row>
-    <row r="264" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A264" s="1">
         <v>43040</v>
       </c>
@@ -41724,18 +39097,8 @@
       <c r="AV264" s="2">
         <v>7.1536779403686523E-2</v>
       </c>
-      <c r="AW264" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX264" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA264">
-        <f t="shared" si="4"/>
-        <v>82.044572260890035</v>
-      </c>
     </row>
-    <row r="265" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A265" s="1">
         <v>43070</v>
       </c>
@@ -41880,18 +39243,8 @@
       <c r="AV265" s="2">
         <v>1.8276523798704147E-2</v>
       </c>
-      <c r="AW265" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX265" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA265">
-        <f t="shared" si="4"/>
-        <v>79.47695355434341</v>
-      </c>
     </row>
-    <row r="266" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A266" s="1">
         <v>43101</v>
       </c>
@@ -42036,18 +39389,8 @@
       <c r="AV266" s="2">
         <v>3.9045553654432297E-2</v>
       </c>
-      <c r="AW266" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX266" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA266">
-        <f t="shared" si="4"/>
-        <v>74.356066919681368</v>
-      </c>
     </row>
-    <row r="267" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A267" s="1">
         <v>43132</v>
       </c>
@@ -42192,18 +39535,8 @@
       <c r="AV267" s="2">
         <v>4.6498649753630161E-3</v>
       </c>
-      <c r="AW267" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX267" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA267">
-        <f t="shared" si="4"/>
-        <v>31.688546964948571</v>
-      </c>
     </row>
-    <row r="268" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A268" s="1">
         <v>43160</v>
       </c>
@@ -42348,18 +39681,8 @@
       <c r="AV268" s="2">
         <v>4.4081110507249832E-2</v>
       </c>
-      <c r="AW268" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX268" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA268">
-        <f t="shared" si="4"/>
-        <v>101.54189776797364</v>
-      </c>
     </row>
-    <row r="269" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A269" s="1">
         <v>43191</v>
       </c>
@@ -42504,18 +39827,8 @@
       <c r="AV269" s="2">
         <v>2.159547433257103E-2</v>
       </c>
-      <c r="AW269" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX269" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA269">
-        <f t="shared" si="4"/>
-        <v>118.73548593870358</v>
-      </c>
     </row>
-    <row r="270" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A270" s="1">
         <v>43221</v>
       </c>
@@ -42660,18 +39973,8 @@
       <c r="AV270" s="2">
         <v>6.7232541739940643E-2</v>
       </c>
-      <c r="AW270" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX270" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA270">
-        <f t="shared" si="4"/>
-        <v>163.69340438491392</v>
-      </c>
     </row>
-    <row r="271" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A271" s="1">
         <v>43252</v>
       </c>
@@ -42816,18 +40119,8 @@
       <c r="AV271" s="2">
         <v>8.6737431585788727E-2</v>
       </c>
-      <c r="AW271" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX271" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA271">
-        <f t="shared" si="4"/>
-        <v>126.70435653572831</v>
-      </c>
     </row>
-    <row r="272" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A272" s="1">
         <v>43282</v>
       </c>
@@ -42972,18 +40265,8 @@
       <c r="AV272" s="2">
         <v>4.2693078517913818E-2</v>
       </c>
-      <c r="AW272" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX272" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA272">
-        <f t="shared" si="4"/>
-        <v>111.40935927374242</v>
-      </c>
     </row>
-    <row r="273" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A273" s="1">
         <v>43313</v>
       </c>
@@ -43128,18 +40411,8 @@
       <c r="AV273" s="2">
         <v>0.24185962975025177</v>
       </c>
-      <c r="AW273" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX273" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA273">
-        <f t="shared" si="4"/>
-        <v>104.8425557007683</v>
-      </c>
     </row>
-    <row r="274" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A274" s="1">
         <v>43344</v>
       </c>
@@ -43284,18 +40557,8 @@
       <c r="AV274" s="2">
         <v>2.099958062171936E-2</v>
       </c>
-      <c r="AW274" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX274" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA274">
-        <f t="shared" si="4"/>
-        <v>84.185137249681446</v>
-      </c>
     </row>
-    <row r="275" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A275" s="1">
         <v>43374</v>
       </c>
@@ -43440,18 +40703,8 @@
       <c r="AV275" s="2">
         <v>2.8835063800215721E-2</v>
       </c>
-      <c r="AW275" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX275" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA275">
-        <f t="shared" si="4"/>
-        <v>112.87130600328668</v>
-      </c>
     </row>
-    <row r="276" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A276" s="1">
         <v>43405</v>
       </c>
@@ -43596,18 +40849,8 @@
       <c r="AV276" s="2">
         <v>1.6954181715846062E-2</v>
       </c>
-      <c r="AW276" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX276" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA276">
-        <f t="shared" si="4"/>
-        <v>72.468726560358974</v>
-      </c>
     </row>
-    <row r="277" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A277" s="1">
         <v>43435</v>
       </c>
@@ -43752,18 +40995,8 @@
       <c r="AV277" s="2">
         <v>1.8774935975670815E-2</v>
       </c>
-      <c r="AW277" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX277" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA277">
-        <f t="shared" si="4"/>
-        <v>88.643347688972256</v>
-      </c>
     </row>
-    <row r="278" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A278" s="1">
         <v>43466</v>
       </c>
@@ -43908,18 +41141,8 @@
       <c r="AV278" s="2">
         <v>4.2498938739299774E-2</v>
       </c>
-      <c r="AW278" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX278" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA278">
-        <f t="shared" si="4"/>
-        <v>100.41637139651758</v>
-      </c>
     </row>
-    <row r="279" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A279" s="1">
         <v>43497</v>
       </c>
@@ -44064,18 +41287,8 @@
       <c r="AV279" s="2">
         <v>1.4162968844175339E-2</v>
       </c>
-      <c r="AW279" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX279" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA279">
-        <f t="shared" si="4"/>
-        <v>116.15861788572812</v>
-      </c>
     </row>
-    <row r="280" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A280" s="1">
         <v>43525</v>
       </c>
@@ -44220,18 +41433,8 @@
       <c r="AV280" s="2">
         <v>2.0855927839875221E-2</v>
       </c>
-      <c r="AW280" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX280" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA280">
-        <f t="shared" si="4"/>
-        <v>83.813314215983624</v>
-      </c>
     </row>
-    <row r="281" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A281" s="1">
         <v>43556</v>
       </c>
@@ -44376,18 +41579,8 @@
       <c r="AV281" s="2">
         <v>3.1336735934019089E-2</v>
       </c>
-      <c r="AW281" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX281" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA281">
-        <f t="shared" si="4"/>
-        <v>60.652286261900336</v>
-      </c>
     </row>
-    <row r="282" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A282" s="1">
         <v>43586</v>
       </c>
@@ -44532,18 +41725,8 @@
       <c r="AV282" s="2">
         <v>2.1490586921572685E-2</v>
       </c>
-      <c r="AW282" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX282" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA282">
-        <f t="shared" si="4"/>
-        <v>126.53444332831401</v>
-      </c>
     </row>
-    <row r="283" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A283" s="1">
         <v>43617</v>
       </c>
@@ -44688,18 +41871,8 @@
       <c r="AV283" s="2">
         <v>5.1773231476545334E-2</v>
       </c>
-      <c r="AW283" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX283" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA283">
-        <f t="shared" si="4"/>
-        <v>140.06578383492234</v>
-      </c>
     </row>
-    <row r="284" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A284" s="1">
         <v>43647</v>
       </c>
@@ -44844,18 +42017,8 @@
       <c r="AV284" s="2">
         <v>2.6546323671936989E-2</v>
       </c>
-      <c r="AW284" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX284" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA284">
-        <f t="shared" si="4"/>
-        <v>82.31183177797034</v>
-      </c>
     </row>
-    <row r="285" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A285" s="1">
         <v>43678</v>
       </c>
@@ -45000,18 +42163,8 @@
       <c r="AV285" s="2">
         <v>4.4243872165679932E-2</v>
       </c>
-      <c r="AW285" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX285" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA285">
-        <f t="shared" si="4"/>
-        <v>132.05717573904417</v>
-      </c>
     </row>
-    <row r="286" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A286" s="1">
         <v>43709</v>
       </c>
@@ -45156,18 +42309,8 @@
       <c r="AV286" s="2">
         <v>2.6573365554213524E-2</v>
       </c>
-      <c r="AW286" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX286" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA286">
-        <f t="shared" si="4"/>
-        <v>79.182036839265805</v>
-      </c>
     </row>
-    <row r="287" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A287" s="1">
         <v>43739</v>
       </c>
@@ -45312,18 +42455,8 @@
       <c r="AV287" s="2">
         <v>2.9429076239466667E-2</v>
       </c>
-      <c r="AW287" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX287" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA287">
-        <f t="shared" si="4"/>
-        <v>73.119327970355812</v>
-      </c>
     </row>
-    <row r="288" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A288" s="1">
         <v>43770</v>
       </c>
@@ -45468,18 +42601,8 @@
       <c r="AV288" s="2">
         <v>2.6408450677990913E-2</v>
       </c>
-      <c r="AW288" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX288" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA288">
-        <f t="shared" si="4"/>
-        <v>65.298728804075353</v>
-      </c>
     </row>
-    <row r="289" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A289" s="1">
         <v>43800</v>
       </c>
@@ -45624,18 +42747,8 @@
       <c r="AV289" s="2">
         <v>1.456169318407774E-2</v>
       </c>
-      <c r="AW289" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX289" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA289">
-        <f t="shared" si="4"/>
-        <v>64.857045197159536</v>
-      </c>
     </row>
-    <row r="290" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A290" s="1">
         <v>43831</v>
       </c>
@@ -45780,18 +42893,8 @@
       <c r="AV290" s="2">
         <v>1.3236267492175102E-2</v>
       </c>
-      <c r="AW290" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX290" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA290">
-        <f t="shared" si="4"/>
-        <v>134.81173545640672</v>
-      </c>
     </row>
-    <row r="291" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A291" s="1">
         <v>43862</v>
       </c>
@@ -45936,18 +43039,8 @@
       <c r="AV291" s="2">
         <v>4.9041461199522018E-2</v>
       </c>
-      <c r="AW291" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX291" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA291">
-        <f t="shared" si="4"/>
-        <v>94.166049940129639</v>
-      </c>
     </row>
-    <row r="292" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A292" s="1">
         <v>43891</v>
       </c>
@@ -46092,18 +43185,8 @@
       <c r="AV292" s="2">
         <v>3.4205574542284012E-2</v>
       </c>
-      <c r="AW292" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX292" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA292">
-        <f t="shared" si="4"/>
-        <v>72.276340675577018</v>
-      </c>
     </row>
-    <row r="293" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A293" s="1">
         <v>43922</v>
       </c>
@@ -46248,18 +43331,8 @@
       <c r="AV293" s="2">
         <v>3.7138480693101883E-2</v>
       </c>
-      <c r="AW293" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX293" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA293">
-        <f t="shared" si="4"/>
-        <v>64.706307272614012</v>
-      </c>
     </row>
-    <row r="294" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A294" s="1">
         <v>43952</v>
       </c>
@@ -46404,18 +43477,8 @@
       <c r="AV294" s="2">
         <v>1.3518384657800198E-2</v>
       </c>
-      <c r="AW294" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX294" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA294">
-        <f t="shared" si="4"/>
-        <v>81.209649817127811</v>
-      </c>
     </row>
-    <row r="295" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A295" s="1">
         <v>43983</v>
       </c>
@@ -46560,18 +43623,8 @@
       <c r="AV295" s="2">
         <v>8.3056479692459106E-2</v>
       </c>
-      <c r="AW295" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX295" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA295">
-        <f t="shared" si="4"/>
-        <v>81.933526022791142</v>
-      </c>
     </row>
-    <row r="296" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A296" s="1">
         <v>44013</v>
       </c>
@@ -46716,18 +43769,8 @@
       <c r="AV296" s="2">
         <v>1.800261065363884E-2</v>
       </c>
-      <c r="AW296" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX296" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA296">
-        <f t="shared" si="4"/>
-        <v>98.29767147093726</v>
-      </c>
     </row>
-    <row r="297" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A297" s="1">
         <v>44044</v>
       </c>
@@ -46872,18 +43915,8 @@
       <c r="AV297" s="2">
         <v>2.6715347543358803E-2</v>
       </c>
-      <c r="AW297" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX297" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA297">
-        <f t="shared" si="4"/>
-        <v>70.319723200803381</v>
-      </c>
     </row>
-    <row r="298" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A298" s="1">
         <v>44075</v>
       </c>
@@ -47028,18 +44061,8 @@
       <c r="AV298" s="2">
         <v>3.1367629766464233E-2</v>
       </c>
-      <c r="AW298" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX298" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA298">
-        <f t="shared" si="4"/>
-        <v>90.752413231794776</v>
-      </c>
     </row>
-    <row r="299" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A299" s="1">
         <v>44105</v>
       </c>
@@ -47184,18 +44207,8 @@
       <c r="AV299" s="2">
         <v>4.2181634344160557E-3</v>
       </c>
-      <c r="AW299" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX299" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA299">
-        <f t="shared" si="4"/>
-        <v>68.414565032942903</v>
-      </c>
     </row>
-    <row r="300" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A300" s="1">
         <v>44136</v>
       </c>
@@ -47340,18 +44353,8 @@
       <c r="AV300" s="2">
         <v>7.8006699681282043E-2</v>
       </c>
-      <c r="AW300" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX300" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA300">
-        <f t="shared" si="4"/>
-        <v>43.743150180769021</v>
-      </c>
     </row>
-    <row r="301" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A301" s="1">
         <v>44166</v>
       </c>
@@ -47496,18 +44499,8 @@
       <c r="AV301" s="2">
         <v>4.249291867017746E-2</v>
       </c>
-      <c r="AW301" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX301" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA301">
-        <f t="shared" si="4"/>
-        <v>61.721736061861876</v>
-      </c>
     </row>
-    <row r="302" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A302" s="1">
         <v>44197</v>
       </c>
@@ -47652,18 +44645,8 @@
       <c r="AV302" s="2">
         <v>4.8653192818164825E-2</v>
       </c>
-      <c r="AW302" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX302" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA302">
-        <f t="shared" si="4"/>
-        <v>79.770718526934075</v>
-      </c>
     </row>
-    <row r="303" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A303" s="1">
         <v>44228</v>
       </c>
@@ -47808,18 +44791,8 @@
       <c r="AV303" s="2">
         <v>3.866228461265564E-2</v>
       </c>
-      <c r="AW303" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX303" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA303">
-        <f t="shared" si="4"/>
-        <v>73.448011452095528</v>
-      </c>
     </row>
-    <row r="304" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A304" s="1">
         <v>44256</v>
       </c>
@@ -47964,18 +44937,8 @@
       <c r="AV304" s="2">
         <v>9.6069872379302979E-2</v>
       </c>
-      <c r="AW304" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX304" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA304">
-        <f t="shared" si="4"/>
-        <v>85.683061172859837</v>
-      </c>
     </row>
-    <row r="305" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A305" s="1">
         <v>44287</v>
       </c>
@@ -48120,18 +45083,8 @@
       <c r="AV305" s="2">
         <v>7.4491366744041443E-2</v>
       </c>
-      <c r="AW305" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX305" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA305">
-        <f t="shared" si="4"/>
-        <v>74.976010112345676</v>
-      </c>
     </row>
-    <row r="306" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A306" s="1">
         <v>44317</v>
       </c>
@@ -48276,18 +45229,8 @@
       <c r="AV306" s="2">
         <v>4.089050367474556E-2</v>
       </c>
-      <c r="AW306" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX306" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA306">
-        <f t="shared" si="4"/>
-        <v>64.527015833738545</v>
-      </c>
     </row>
-    <row r="307" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A307" s="1">
         <v>44348</v>
       </c>
@@ -48432,18 +45375,8 @@
       <c r="AV307" s="2">
         <v>4.6416636556386948E-2</v>
       </c>
-      <c r="AW307" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX307" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA307">
-        <f t="shared" si="4"/>
-        <v>73.426754507561398</v>
-      </c>
     </row>
-    <row r="308" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A308" s="1">
         <v>44378</v>
       </c>
@@ -48588,18 +45521,8 @@
       <c r="AV308" s="2">
         <v>3.5851933062076569E-2</v>
       </c>
-      <c r="AW308" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX308" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA308">
-        <f t="shared" si="4"/>
-        <v>52.557229442319432</v>
-      </c>
     </row>
-    <row r="309" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A309" s="1">
         <v>44409</v>
       </c>
@@ -48744,18 +45667,8 @@
       <c r="AV309" s="2">
         <v>2.8964517638087273E-2</v>
       </c>
-      <c r="AW309" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX309" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA309">
-        <f t="shared" si="4"/>
-        <v>58.478676075472926</v>
-      </c>
     </row>
-    <row r="310" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A310" s="1">
         <v>44440</v>
       </c>
@@ -48900,18 +45813,8 @@
       <c r="AV310" s="2">
         <v>1.8726591020822525E-2</v>
       </c>
-      <c r="AW310" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX310" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA310">
-        <f t="shared" si="4"/>
-        <v>82.510613434064723</v>
-      </c>
     </row>
-    <row r="311" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A311" s="1">
         <v>44470</v>
       </c>
@@ -49056,18 +45959,8 @@
       <c r="AV311" s="2">
         <v>4.0327999740839005E-2</v>
       </c>
-      <c r="AW311" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX311" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA311">
-        <f t="shared" si="4"/>
-        <v>74.729420384836985</v>
-      </c>
     </row>
-    <row r="312" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A312" s="1">
         <v>44501</v>
       </c>
@@ -49212,18 +46105,8 @@
       <c r="AV312" s="2">
         <v>9.0026058256626129E-2</v>
       </c>
-      <c r="AW312" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX312" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA312">
-        <f t="shared" si="4"/>
-        <v>77.673633606411997</v>
-      </c>
     </row>
-    <row r="313" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A313" s="1">
         <v>44531</v>
       </c>
@@ -49368,18 +46251,8 @@
       <c r="AV313" s="2">
         <v>5.9244632720947266E-2</v>
       </c>
-      <c r="AW313" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX313" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA313">
-        <f t="shared" si="4"/>
-        <v>83.898216796724697</v>
-      </c>
     </row>
-    <row r="314" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A314" s="1">
         <v>44562</v>
       </c>
@@ -49524,18 +46397,8 @@
       <c r="AV314" s="2">
         <v>6.7868918180465698E-2</v>
       </c>
-      <c r="AW314" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX314" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA314">
-        <f t="shared" si="4"/>
-        <v>76.927646778688214</v>
-      </c>
     </row>
-    <row r="315" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A315" s="1">
         <v>44593</v>
       </c>
@@ -49680,18 +46543,8 @@
       <c r="AV315" s="2">
         <v>5.5370986461639404E-2</v>
       </c>
-      <c r="AW315" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX315" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA315">
-        <f t="shared" si="4"/>
-        <v>144.38768898784954</v>
-      </c>
     </row>
-    <row r="316" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A316" s="1">
         <v>44621</v>
       </c>
@@ -49836,18 +46689,8 @@
       <c r="AV316" s="2">
         <v>9.6292726695537567E-2</v>
       </c>
-      <c r="AW316" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX316" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA316">
-        <f t="shared" si="4"/>
-        <v>240.68961522588063</v>
-      </c>
     </row>
-    <row r="317" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A317" s="1">
         <v>44652</v>
       </c>
@@ -49992,18 +46835,8 @@
       <c r="AV317" s="2">
         <v>8.1651695072650909E-2</v>
       </c>
-      <c r="AW317" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX317" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA317">
-        <f t="shared" si="4"/>
-        <v>113.27191490823347</v>
-      </c>
     </row>
-    <row r="318" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A318" s="1">
         <v>44682</v>
       </c>
@@ -50148,18 +46981,8 @@
       <c r="AV318" s="2">
         <v>5.0930902361869812E-2</v>
       </c>
-      <c r="AW318" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX318" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA318">
-        <f t="shared" si="4"/>
-        <v>101.6938709309334</v>
-      </c>
     </row>
-    <row r="319" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A319" s="1">
         <v>44713</v>
       </c>
@@ -50304,18 +47127,8 @@
       <c r="AV319" s="2">
         <v>5.8865081518888474E-2</v>
       </c>
-      <c r="AW319" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX319" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA319">
-        <f t="shared" si="4"/>
-        <v>86.207607903404067</v>
-      </c>
     </row>
-    <row r="320" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A320" s="1">
         <v>44743</v>
       </c>
@@ -50460,18 +47273,8 @@
       <c r="AV320" s="2">
         <v>4.6473801136016846E-2</v>
       </c>
-      <c r="AW320" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX320" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA320">
-        <f t="shared" si="4"/>
-        <v>81.852676365504749</v>
-      </c>
     </row>
-    <row r="321" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A321" s="1">
         <v>44774</v>
       </c>
@@ -50616,18 +47419,8 @@
       <c r="AV321" s="2">
         <v>5.3292278200387955E-2</v>
       </c>
-      <c r="AW321" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX321" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA321">
-        <f t="shared" si="4"/>
-        <v>123.96116400518665</v>
-      </c>
     </row>
-    <row r="322" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A322" s="1">
         <v>44805</v>
       </c>
@@ -50772,18 +47565,8 @@
       <c r="AV322" s="2">
         <v>3.5346098244190216E-2</v>
       </c>
-      <c r="AW322" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX322" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA322">
-        <f t="shared" si="4"/>
-        <v>114.62694653914434</v>
-      </c>
     </row>
-    <row r="323" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A323" s="1">
         <v>44835</v>
       </c>
@@ -50928,18 +47711,8 @@
       <c r="AV323" s="2">
         <v>4.5439053326845169E-2</v>
       </c>
-      <c r="AW323" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX323" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA323">
-        <f t="shared" ref="BA323:BA358" si="5">(L323/AVERAGE(L323:L679))*100</f>
-        <v>119.5941666194749</v>
-      </c>
     </row>
-    <row r="324" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A324" s="1">
         <v>44866</v>
       </c>
@@ -51084,18 +47857,8 @@
       <c r="AV324" s="2">
         <v>7.4120528995990753E-2</v>
       </c>
-      <c r="AW324" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX324" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA324">
-        <f t="shared" si="5"/>
-        <v>113.7618839049594</v>
-      </c>
     </row>
-    <row r="325" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A325" s="1">
         <v>44896</v>
       </c>
@@ -51240,18 +48003,8 @@
       <c r="AV325" s="2">
         <v>3.7195462733507156E-2</v>
       </c>
-      <c r="AW325" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX325" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA325">
-        <f t="shared" si="5"/>
-        <v>89.343868402396467</v>
-      </c>
     </row>
-    <row r="326" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A326" s="1">
         <v>44927</v>
       </c>
@@ -51396,18 +48149,8 @@
       <c r="AV326" s="2">
         <v>3.790750727057457E-2</v>
       </c>
-      <c r="AW326" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX326" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA326">
-        <f t="shared" si="5"/>
-        <v>68.231766296673399</v>
-      </c>
     </row>
-    <row r="327" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A327" s="1">
         <v>44958</v>
       </c>
@@ -51552,18 +48295,8 @@
       <c r="AV327" s="2">
         <v>9.3395598232746124E-2</v>
       </c>
-      <c r="AW327" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX327" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA327">
-        <f t="shared" si="5"/>
-        <v>150.07895055713138</v>
-      </c>
     </row>
-    <row r="328" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A328" s="1">
         <v>44986</v>
       </c>
@@ -51708,18 +48441,8 @@
       <c r="AV328" s="2">
         <v>6.4866140484809875E-2</v>
       </c>
-      <c r="AW328" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX328" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA328">
-        <f t="shared" si="5"/>
-        <v>144.51500652762886</v>
-      </c>
     </row>
-    <row r="329" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A329" s="1">
         <v>45017</v>
       </c>
@@ -51864,18 +48587,8 @@
       <c r="AV329" s="2">
         <v>5.1880676299333572E-2</v>
       </c>
-      <c r="AW329" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX329" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA329">
-        <f t="shared" si="5"/>
-        <v>127.57324387284265</v>
-      </c>
     </row>
-    <row r="330" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A330" s="1">
         <v>45047</v>
       </c>
@@ -52020,18 +48733,8 @@
       <c r="AV330" s="2">
         <v>0.18175208568572998</v>
       </c>
-      <c r="AW330" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX330" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA330">
-        <f t="shared" si="5"/>
-        <v>113.95736654707702</v>
-      </c>
     </row>
-    <row r="331" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A331" s="1">
         <v>45078</v>
       </c>
@@ -52176,18 +48879,8 @@
       <c r="AV331" s="2">
         <v>0.1223316416144371</v>
       </c>
-      <c r="AW331" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX331" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA331">
-        <f t="shared" si="5"/>
-        <v>111.75227212865408</v>
-      </c>
     </row>
-    <row r="332" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A332" s="1">
         <v>45108</v>
       </c>
@@ -52332,18 +49025,8 @@
       <c r="AV332" s="2">
         <v>0.11177347600460052</v>
       </c>
-      <c r="AW332" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX332" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA332">
-        <f t="shared" si="5"/>
-        <v>103.40983297205446</v>
-      </c>
     </row>
-    <row r="333" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A333" s="1">
         <v>45139</v>
       </c>
@@ -52488,18 +49171,8 @@
       <c r="AV333" s="2">
         <v>0.13347893953323364</v>
       </c>
-      <c r="AW333" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX333" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA333">
-        <f t="shared" si="5"/>
-        <v>105.03730718625827</v>
-      </c>
     </row>
-    <row r="334" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A334" s="1">
         <v>45170</v>
       </c>
@@ -52644,18 +49317,8 @@
       <c r="AV334" s="2">
         <v>0.11494947969913483</v>
       </c>
-      <c r="AW334" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX334" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA334">
-        <f t="shared" si="5"/>
-        <v>115.25195063731269</v>
-      </c>
     </row>
-    <row r="335" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A335" s="1">
         <v>45200</v>
       </c>
@@ -52800,18 +49463,8 @@
       <c r="AV335" s="2">
         <v>6.5683409571647644E-2</v>
       </c>
-      <c r="AW335" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX335" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA335">
-        <f t="shared" si="5"/>
-        <v>111.28145706424321</v>
-      </c>
     </row>
-    <row r="336" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A336" s="1">
         <v>45231</v>
       </c>
@@ -52956,18 +49609,8 @@
       <c r="AV336" s="2">
         <v>5.6323926895856857E-2</v>
       </c>
-      <c r="AW336" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX336" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA336">
-        <f t="shared" si="5"/>
-        <v>99.017914001396136</v>
-      </c>
     </row>
-    <row r="337" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A337" s="1">
         <v>45261</v>
       </c>
@@ -53112,18 +49755,8 @@
       <c r="AV337" s="2">
         <v>0.11585994064807892</v>
       </c>
-      <c r="AW337" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX337" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA337">
-        <f t="shared" si="5"/>
-        <v>75.481322900932483</v>
-      </c>
     </row>
-    <row r="338" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A338" s="1">
         <v>45292</v>
       </c>
@@ -53268,18 +49901,8 @@
       <c r="AV338" s="2">
         <v>0.30063885450363159</v>
       </c>
-      <c r="AW338" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX338" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA338">
-        <f t="shared" si="5"/>
-        <v>103.23964794310186</v>
-      </c>
     </row>
-    <row r="339" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A339" s="1">
         <v>45323</v>
       </c>
@@ -53424,18 +50047,8 @@
       <c r="AV339" s="2">
         <v>0.12432114034891129</v>
       </c>
-      <c r="AW339" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX339" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA339">
-        <f t="shared" si="5"/>
-        <v>82.241002502786685</v>
-      </c>
     </row>
-    <row r="340" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A340" s="1">
         <v>45352</v>
       </c>
@@ -53580,18 +50193,8 @@
       <c r="AV340" s="2">
         <v>0.11679370701313019</v>
       </c>
-      <c r="AW340" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX340" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA340">
-        <f t="shared" si="5"/>
-        <v>92.763351514404704</v>
-      </c>
     </row>
-    <row r="341" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A341" s="1">
         <v>45383</v>
       </c>
@@ -53736,18 +50339,8 @@
       <c r="AV341" s="2">
         <v>0.13923169672489166</v>
       </c>
-      <c r="AW341" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX341" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA341">
-        <f t="shared" si="5"/>
-        <v>109.7567976985369</v>
-      </c>
     </row>
-    <row r="342" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A342" s="1">
         <v>45413</v>
       </c>
@@ -53892,18 +50485,8 @@
       <c r="AV342" s="2">
         <v>0.17739172279834747</v>
       </c>
-      <c r="AW342" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX342" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA342">
-        <f t="shared" si="5"/>
-        <v>98.936963181030393</v>
-      </c>
     </row>
-    <row r="343" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A343" s="1">
         <v>45444</v>
       </c>
@@ -54048,18 +50631,8 @@
       <c r="AV343" s="2">
         <v>0.1141263023018837</v>
       </c>
-      <c r="AW343" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX343" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA343">
-        <f t="shared" si="5"/>
-        <v>94.444278430588739</v>
-      </c>
     </row>
-    <row r="344" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A344" s="1">
         <v>45474</v>
       </c>
@@ -54204,18 +50777,8 @@
       <c r="AV344" s="2">
         <v>5.5425543338060379E-2</v>
       </c>
-      <c r="AW344" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX344" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA344">
-        <f t="shared" si="5"/>
-        <v>77.135122851284322</v>
-      </c>
     </row>
-    <row r="345" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A345" s="1">
         <v>45505</v>
       </c>
@@ -54360,18 +50923,8 @@
       <c r="AV345" s="2">
         <v>6.329914927482605E-2</v>
       </c>
-      <c r="AW345" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX345" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA345">
-        <f t="shared" si="5"/>
-        <v>66.209665748993189</v>
-      </c>
     </row>
-    <row r="346" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A346" s="1">
         <v>45536</v>
       </c>
@@ -54516,18 +51069,8 @@
       <c r="AV346" s="2">
         <v>7.156333327293396E-2</v>
       </c>
-      <c r="AW346" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX346" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA346">
-        <f t="shared" si="5"/>
-        <v>77.488595914110675</v>
-      </c>
     </row>
-    <row r="347" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A347" s="1">
         <v>45566</v>
       </c>
@@ -54672,18 +51215,8 @@
       <c r="AV347" s="2">
         <v>0.14838629961013794</v>
       </c>
-      <c r="AW347" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX347" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA347">
-        <f t="shared" si="5"/>
-        <v>96.788976296389947</v>
-      </c>
     </row>
-    <row r="348" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A348" s="1">
         <v>45597</v>
       </c>
@@ -54828,18 +51361,8 @@
       <c r="AV348" s="2">
         <v>9.4452492892742157E-2</v>
       </c>
-      <c r="AW348" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX348" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA348">
-        <f t="shared" si="5"/>
-        <v>98.287790299675464</v>
-      </c>
     </row>
-    <row r="349" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A349" s="1">
         <v>45627</v>
       </c>
@@ -54984,18 +51507,8 @@
       <c r="AV349" s="2">
         <v>0.10431879758834839</v>
       </c>
-      <c r="AW349" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX349" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA349">
-        <f t="shared" si="5"/>
-        <v>82.991584556070606</v>
-      </c>
     </row>
-    <row r="350" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A350" s="1">
         <v>45658</v>
       </c>
@@ -55140,18 +51653,8 @@
       <c r="AV350" s="2">
         <v>8.1560954451560974E-2</v>
       </c>
-      <c r="AW350" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX350" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA350">
-        <f t="shared" si="5"/>
-        <v>82.589412376633746</v>
-      </c>
     </row>
-    <row r="351" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A351" s="1">
         <v>45689</v>
       </c>
@@ -55296,18 +51799,8 @@
       <c r="AV351" s="2">
         <v>7.4153967201709747E-2</v>
       </c>
-      <c r="AW351" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX351" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA351">
-        <f t="shared" si="5"/>
-        <v>104.73259169412552</v>
-      </c>
     </row>
-    <row r="352" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A352" s="1">
         <v>45717</v>
       </c>
@@ -55452,18 +51945,8 @@
       <c r="AV352" s="2">
         <v>7.711472362279892E-2</v>
       </c>
-      <c r="AW352" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX352" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA352">
-        <f t="shared" si="5"/>
-        <v>102.96931068812812</v>
-      </c>
     </row>
-    <row r="353" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A353" s="1">
         <v>45748</v>
       </c>
@@ -55608,18 +52091,8 @@
       <c r="AV353" s="2">
         <v>0.11539629846811295</v>
       </c>
-      <c r="AW353" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX353" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA353">
-        <f t="shared" si="5"/>
-        <v>98.965586777881256</v>
-      </c>
     </row>
-    <row r="354" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A354" s="1">
         <v>45778</v>
       </c>
@@ -55764,18 +52237,8 @@
       <c r="AV354" s="2">
         <v>9.3836136162281036E-2</v>
       </c>
-      <c r="AW354" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX354" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA354">
-        <f t="shared" si="5"/>
-        <v>108.83068155169437</v>
-      </c>
     </row>
-    <row r="355" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A355" s="1">
         <v>45809</v>
       </c>
@@ -55920,18 +52383,8 @@
       <c r="AV355" s="2">
         <v>3.7401821464300156E-2</v>
       </c>
-      <c r="AW355" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX355" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA355">
-        <f t="shared" si="5"/>
-        <v>135.96935521371572</v>
-      </c>
     </row>
-    <row r="356" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A356" s="1">
         <v>45839</v>
       </c>
@@ -56076,18 +52529,8 @@
       <c r="AV356" s="2">
         <v>5.029548704624176E-2</v>
       </c>
-      <c r="AW356" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX356" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA356">
-        <f t="shared" si="5"/>
-        <v>101.31380484875956</v>
-      </c>
     </row>
-    <row r="357" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A357" s="1">
         <v>45870</v>
       </c>
@@ -56232,18 +52675,8 @@
       <c r="AV357" s="2">
         <v>7.1576841175556183E-2</v>
       </c>
-      <c r="AW357" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX357" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA357">
-        <f t="shared" si="5"/>
-        <v>97.691383566508378</v>
-      </c>
     </row>
-    <row r="358" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A358" s="1">
         <v>45901</v>
       </c>
@@ -56387,16 +52820,6 @@
       </c>
       <c r="AV358" s="2">
         <v>8.1652648746967316E-2</v>
-      </c>
-      <c r="AW358" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX358" t="s">
-        <v>48</v>
-      </c>
-      <c r="BA358">
-        <f t="shared" si="5"/>
-        <v>100</v>
       </c>
     </row>
   </sheetData>
